--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.1%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.4%</t>
+          <t>452.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-631.0%</t>
+          <t>-630.0%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.4%</t>
+          <t>-42.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-240.6%</t>
+          <t>-240.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.35</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-30.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.5%</t>
+          <t>-226.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-116.3%</t>
+          <t>-124.2%</t>
         </is>
       </c>
     </row>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.823478562726693</v>
+        <v>-4.721563258226239</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7927272825737446</v>
+        <v>0.8334934043739262</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1037690524253604</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.785094900168542</v>
+        <v>-4.683179595668088</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8055001889393736</v>
+        <v>0.8462663107395554</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.06538538986720921</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.607978570133376</v>
+        <v>-4.506063265632922</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.873075749798742</v>
+        <v>0.9138418715989236</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.06538538986720921</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.653070814966922</v>
+        <v>-4.551155510466468</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8557222436272367</v>
+        <v>0.8964883654274185</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.127281433036599</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.473695393728154</v>
+        <v>-4.3717800892277</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9212593874291581</v>
+        <v>0.9620255092293399</v>
       </c>
       <c r="F1957" t="n">
         <v>0.02949532513411968</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.51870960724876</v>
+        <v>-4.416794302748307</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8840611573525057</v>
+        <v>0.924827279152687</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.0008535701804849305</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.785714117521195</v>
+        <v>-4.683798813020742</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7829509155824774</v>
+        <v>0.8237170373826588</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1952166082234335</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.886911898958368</v>
+        <v>-4.784996594457914</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7416757249041097</v>
+        <v>0.7824418467042911</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2636254217687527</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.854436312787596</v>
+        <v>-4.752521008287142</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7522659209267353</v>
+        <v>0.7930320427269166</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2636254217687527</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.835398185080298</v>
+        <v>-4.733482880579845</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7564058912178993</v>
+        <v>0.7971720130180806</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3218090330999472</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.866524816230917</v>
+        <v>-4.764609511730463</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9215371076963323</v>
+        <v>0.9623032294965137</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3218090330999472</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.880391577564835</v>
+        <v>-4.778476273064381</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9168237321488988</v>
+        <v>0.9575898539490801</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3596669498337702</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.900648876093793</v>
+        <v>-4.798733571593339</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9147293431342416</v>
+        <v>0.9554954649344229</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3596669498337702</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.75290590585879</v>
+        <v>-4.650990601358337</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.052979179020264</v>
+        <v>1.093745300820446</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.191859592598887</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.854920588390011</v>
+        <v>-4.753005283889558</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.014966927539257</v>
+        <v>1.055733049339438</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.191859592598887</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.848767882337227</v>
+        <v>-4.746852577836774</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.018090358352029</v>
+        <v>1.05885648015221</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1857068865461027</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.865577180487729</v>
+        <v>-4.763661875987276</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.010447115831939</v>
+        <v>1.05121323763212</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2025161846966044</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.803279181711607</v>
+        <v>-4.701363877211153</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.101701869139208</v>
+        <v>1.14246799093939</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2025161846966044</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.601488984046449</v>
+        <v>-4.499573679545995</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8909988205946695</v>
+        <v>0.9317649423948509</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.004497992527449979</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.541598302403855</v>
+        <v>-4.439682997903402</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.985245325573882</v>
+        <v>1.026011447374063</v>
       </c>
       <c r="F1972" t="n">
         <v>0.0553926891151435</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.63933884702883</v>
+        <v>-4.537423542528376</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.960776843839936</v>
+        <v>1.001542965640117</v>
       </c>
       <c r="F1973" t="n">
         <v>0.03950341098216331</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.815676607151759</v>
+        <v>-4.713761302651306</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8887777206154359</v>
+        <v>0.9295438424156173</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1368343491407661</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.744130284374882</v>
+        <v>-4.642214979874429</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9158878677661153</v>
+        <v>0.9566539895662967</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1368343491407661</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.699757152736313</v>
+        <v>-4.59784184823586</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.933499987856979</v>
+        <v>0.9742661096571603</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.09246121750219749</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.691803182441541</v>
+        <v>-4.589887877941088</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9366815759748879</v>
+        <v>0.977447697775069</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.09246121750219749</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.644147451880485</v>
+        <v>-4.542232147380032</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9621256252271149</v>
+        <v>1.002891747027296</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.04480548694114184</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.516463142086189</v>
+        <v>-4.414547837585736</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.018091722519558</v>
+        <v>1.058857844319739</v>
       </c>
       <c r="F1979" t="n">
         <v>0.08287882285315462</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.577129732488578</v>
+        <v>-4.475214427988125</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9805797588344745</v>
+        <v>1.021345880634656</v>
       </c>
       <c r="F1980" t="n">
         <v>0.001180506134620951</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.53229133088018</v>
+        <v>-4.430376026379727</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.002612822088462</v>
+        <v>1.043378943888644</v>
       </c>
       <c r="F1981" t="n">
         <v>0.005723939079490425</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.633049966637178</v>
+        <v>-4.531134662136725</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9664703074167413</v>
+        <v>1.007236429216923</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.083101629647515</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.588847129551278</v>
+        <v>-4.486931825050824</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9900310447789387</v>
+        <v>1.03079716657912</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.03889879256161455</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.62582615721472</v>
+        <v>-4.523910852714267</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.973649434182809</v>
+        <v>1.01441555598299</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.001924890770284016</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.645884236079561</v>
+        <v>-4.543968931579108</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.016873967819913</v>
+        <v>1.057640089620094</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.001924890770284016</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.605953562901671</v>
+        <v>-4.504038258401217</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.031286941685322</v>
+        <v>1.072053063485503</v>
       </c>
       <c r="F1986" t="n">
         <v>0.03800578240760633</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.565483215338966</v>
+        <v>-4.463567910838512</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.042423308948674</v>
+        <v>1.083189430748855</v>
       </c>
       <c r="F1987" t="n">
         <v>0.07847612997031128</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.50025903421176</v>
+        <v>-4.398343729711307</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.085700385492261</v>
+        <v>1.126466507292442</v>
       </c>
       <c r="F1988" t="n">
         <v>0.1437003110975169</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.550753324568817</v>
+        <v>-4.448838020068363</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.061463641648719</v>
+        <v>1.1022297634489</v>
       </c>
       <c r="F1989" t="n">
         <v>0.09867957397144267</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.570864980603525</v>
+        <v>-4.468949676103072</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.054675771566076</v>
+        <v>1.095441893366257</v>
       </c>
       <c r="F1990" t="n">
         <v>0.1097069189688619</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.668545559876171</v>
+        <v>-4.566630255375718</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.176161310878228</v>
+        <v>1.216927432678409</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.0009962763713269318</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.644753991270028</v>
+        <v>-4.542838686769575</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.305790847538502</v>
+        <v>1.346556969338684</v>
       </c>
       <c r="F1992" t="n">
         <v>0.02279529223481536</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.681508409831751</v>
+        <v>-4.579593105331297</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.282797056127672</v>
+        <v>1.323563177927854</v>
       </c>
       <c r="F1993" t="n">
         <v>0.02279529223481536</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.677174106774703</v>
+        <v>-4.57525880227425</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.282723972934271</v>
+        <v>1.323490094734452</v>
       </c>
       <c r="F1994" t="n">
         <v>0.1744453955540193</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.66828164538142</v>
+        <v>-4.566366340880966</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.303835363218375</v>
+        <v>1.344601485018557</v>
       </c>
       <c r="F1995" t="n">
         <v>0.1744453955540193</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.836757762351297</v>
+        <v>-4.734842457850844</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.228299963835009</v>
+        <v>1.26906608563519</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1464975598374385</v>
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.431236795039063</v>
+        <v>3.7486156716724</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.693827917420855</v>
+        <v>-4.684663633871975</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.355884563264029</v>
+        <v>1.359550276683581</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1051186619017559</v>
+        <v>-0.0251396206891048</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.296843351687173</v>
+        <v>3.218688382132656</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>15.0%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-78.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>106.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-74.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.1%</t>
+          <t>448.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.0%</t>
+          <t>-644.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.3%</t>
+          <t>-41.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-240.3%</t>
+          <t>-246.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.5%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-226.5%</t>
+          <t>-209.0%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.5%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-124.2%</t>
+          <t>-113.6%</t>
         </is>
       </c>
     </row>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.721563258226239</v>
+        <v>-4.823478562726693</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8334934043739262</v>
+        <v>0.7927272825737446</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1037690524253604</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.683179595668088</v>
+        <v>-4.785094900168542</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8462663107395554</v>
+        <v>0.8055001889393736</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.06538538986720921</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.506063265632922</v>
+        <v>-4.607978570133376</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9138418715989236</v>
+        <v>0.873075749798742</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.06538538986720921</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.551155510466468</v>
+        <v>-4.653070814966922</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8964883654274185</v>
+        <v>0.8557222436272367</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.127281433036599</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.3717800892277</v>
+        <v>-4.473695393728154</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9620255092293399</v>
+        <v>0.9212593874291581</v>
       </c>
       <c r="F1957" t="n">
         <v>0.02949532513411968</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.416794302748307</v>
+        <v>-4.51870960724876</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.924827279152687</v>
+        <v>0.8840611573525057</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.0008535701804849305</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.683798813020742</v>
+        <v>-4.785714117521195</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8237170373826588</v>
+        <v>0.7829509155824774</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1952166082234335</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.784996594457914</v>
+        <v>-4.886911898958368</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7824418467042911</v>
+        <v>0.7416757249041097</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2636254217687527</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.752521008287142</v>
+        <v>-4.854436312787596</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7930320427269166</v>
+        <v>0.7522659209267353</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2636254217687527</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.733482880579845</v>
+        <v>-4.835398185080298</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7971720130180806</v>
+        <v>0.7564058912178993</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3218090330999472</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.764609511730463</v>
+        <v>-4.866524816230917</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9623032294965137</v>
+        <v>0.9215371076963323</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3218090330999472</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.778476273064381</v>
+        <v>-4.880391577564835</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9575898539490801</v>
+        <v>0.9168237321488988</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3596669498337702</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.798733571593339</v>
+        <v>-4.900648876093793</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9554954649344229</v>
+        <v>0.9147293431342416</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3596669498337702</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.650990601358337</v>
+        <v>-4.75290590585879</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.093745300820446</v>
+        <v>1.052979179020264</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.191859592598887</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.753005283889558</v>
+        <v>-4.854920588390011</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.055733049339438</v>
+        <v>1.014966927539257</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.191859592598887</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.746852577836774</v>
+        <v>-4.848767882337227</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.05885648015221</v>
+        <v>1.018090358352029</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1857068865461027</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.763661875987276</v>
+        <v>-4.865577180487729</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.05121323763212</v>
+        <v>1.010447115831939</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2025161846966044</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.701363877211153</v>
+        <v>-4.803279181711607</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.14246799093939</v>
+        <v>1.101701869139208</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2025161846966044</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.499573679545995</v>
+        <v>-4.601488984046449</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9317649423948509</v>
+        <v>0.8909988205946695</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.004497992527449979</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.439682997903402</v>
+        <v>-4.541598302403855</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.026011447374063</v>
+        <v>0.985245325573882</v>
       </c>
       <c r="F1972" t="n">
         <v>0.0553926891151435</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.537423542528376</v>
+        <v>-4.63933884702883</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.001542965640117</v>
+        <v>0.960776843839936</v>
       </c>
       <c r="F1973" t="n">
         <v>0.03950341098216331</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.713761302651306</v>
+        <v>-4.815676607151759</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9295438424156173</v>
+        <v>0.8887777206154359</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1368343491407661</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.642214979874429</v>
+        <v>-4.744130284374882</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9566539895662967</v>
+        <v>0.9158878677661153</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1368343491407661</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.59784184823586</v>
+        <v>-4.699757152736313</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9742661096571603</v>
+        <v>0.933499987856979</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.09246121750219749</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.589887877941088</v>
+        <v>-4.691803182441541</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.977447697775069</v>
+        <v>0.9366815759748879</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.09246121750219749</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.542232147380032</v>
+        <v>-4.644147451880485</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.002891747027296</v>
+        <v>0.9621256252271149</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.04480548694114184</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.414547837585736</v>
+        <v>-4.516463142086189</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.058857844319739</v>
+        <v>1.018091722519558</v>
       </c>
       <c r="F1979" t="n">
         <v>0.08287882285315462</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.475214427988125</v>
+        <v>-4.577129732488578</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.021345880634656</v>
+        <v>0.9805797588344745</v>
       </c>
       <c r="F1980" t="n">
         <v>0.001180506134620951</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.430376026379727</v>
+        <v>-4.53229133088018</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.043378943888644</v>
+        <v>1.002612822088462</v>
       </c>
       <c r="F1981" t="n">
         <v>0.005723939079490425</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.531134662136725</v>
+        <v>-4.633049966637178</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.007236429216923</v>
+        <v>0.9664703074167413</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.083101629647515</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.486931825050824</v>
+        <v>-4.588847129551278</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.03079716657912</v>
+        <v>0.9900310447789387</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.03889879256161455</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.523910852714267</v>
+        <v>-4.62582615721472</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.01441555598299</v>
+        <v>0.973649434182809</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.001924890770284016</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.543968931579108</v>
+        <v>-4.645884236079561</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.057640089620094</v>
+        <v>1.016873967819913</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.001924890770284016</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.504038258401217</v>
+        <v>-4.605953562901671</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.072053063485503</v>
+        <v>1.031286941685322</v>
       </c>
       <c r="F1986" t="n">
         <v>0.03800578240760633</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.463567910838512</v>
+        <v>-4.565483215338966</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.083189430748855</v>
+        <v>1.042423308948674</v>
       </c>
       <c r="F1987" t="n">
         <v>0.07847612997031128</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.398343729711307</v>
+        <v>-4.50025903421176</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.126466507292442</v>
+        <v>1.085700385492261</v>
       </c>
       <c r="F1988" t="n">
         <v>0.1437003110975169</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.448838020068363</v>
+        <v>-4.550753324568817</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.1022297634489</v>
+        <v>1.061463641648719</v>
       </c>
       <c r="F1989" t="n">
         <v>0.09867957397144267</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.468949676103072</v>
+        <v>-4.570864980603525</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.095441893366257</v>
+        <v>1.054675771566076</v>
       </c>
       <c r="F1990" t="n">
         <v>0.1097069189688619</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.566630255375718</v>
+        <v>-4.668545559876171</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.216927432678409</v>
+        <v>1.176161310878228</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.0009962763713269318</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.542838686769575</v>
+        <v>-4.644753991270028</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.346556969338684</v>
+        <v>1.305790847538502</v>
       </c>
       <c r="F1992" t="n">
         <v>0.02279529223481536</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.579593105331297</v>
+        <v>-4.681508409831751</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.323563177927854</v>
+        <v>1.282797056127672</v>
       </c>
       <c r="F1993" t="n">
         <v>0.02279529223481536</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.57525880227425</v>
+        <v>-4.677174106774703</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.323490094734452</v>
+        <v>1.282723972934271</v>
       </c>
       <c r="F1994" t="n">
         <v>0.1744453955540193</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.566366340880966</v>
+        <v>-4.66828164538142</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.344601485018557</v>
+        <v>1.303835363218375</v>
       </c>
       <c r="F1995" t="n">
         <v>0.1744453955540193</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.734842457850844</v>
+        <v>-4.836757762351297</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.26906608563519</v>
+        <v>1.228299963835009</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1464975598374385</v>
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.7486156716724</v>
+        <v>3.431236795039063</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.684663633871975</v>
+        <v>-4.829366005115927</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.359550276683581</v>
+        <v>1.301669328186</v>
       </c>
       <c r="F1997" t="n">
-        <v>-0.0251396206891048</v>
+        <v>0.150399038524355</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.218688382132656</v>
+        <v>3.324011577660732</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.9%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>46.8%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.3%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.0%</t>
+          <t>106.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.5%</t>
+          <t>124.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.9%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.1%</t>
+          <t>452.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-644.5%</t>
+          <t>-620.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.8%</t>
+          <t>-42.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-246.1%</t>
+          <t>-236.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.0%</t>
+          <t>-213.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-113.6%</t>
+          <t>-116.2%</t>
         </is>
       </c>
     </row>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.823478562726693</v>
+        <v>-4.721563258226239</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7927272825737446</v>
+        <v>0.8334934043739262</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1037690524253604</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.785094900168542</v>
+        <v>-4.683179595668088</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8055001889393736</v>
+        <v>0.8462663107395554</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.06538538986720921</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.607978570133376</v>
+        <v>-4.506063265632922</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.873075749798742</v>
+        <v>0.9138418715989236</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.06538538986720921</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.653070814966922</v>
+        <v>-4.551155510466468</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8557222436272367</v>
+        <v>0.8964883654274185</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.127281433036599</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.473695393728154</v>
+        <v>-4.3717800892277</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9212593874291581</v>
+        <v>0.9620255092293399</v>
       </c>
       <c r="F1957" t="n">
         <v>0.02949532513411968</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.51870960724876</v>
+        <v>-4.416794302748307</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8840611573525057</v>
+        <v>0.924827279152687</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.0008535701804849305</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.785714117521195</v>
+        <v>-4.683798813020742</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7829509155824774</v>
+        <v>0.8237170373826588</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1952166082234335</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.886911898958368</v>
+        <v>-4.784996594457914</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7416757249041097</v>
+        <v>0.7824418467042911</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2636254217687527</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.854436312787596</v>
+        <v>-4.752521008287142</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7522659209267353</v>
+        <v>0.7930320427269166</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2636254217687527</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.835398185080298</v>
+        <v>-4.733482880579845</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7564058912178993</v>
+        <v>0.7971720130180806</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3218090330999472</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.866524816230917</v>
+        <v>-4.764609511730463</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9215371076963323</v>
+        <v>0.9623032294965137</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3218090330999472</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.880391577564835</v>
+        <v>-4.778476273064381</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9168237321488988</v>
+        <v>0.9575898539490801</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3596669498337702</v>
@@ -46746,10 +46746,10 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.900648876093793</v>
+        <v>-4.798733571593339</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9147293431342416</v>
+        <v>0.9554954649344229</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3596669498337702</v>
@@ -46769,10 +46769,10 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.75290590585879</v>
+        <v>-4.650990601358337</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.052979179020264</v>
+        <v>1.093745300820446</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.191859592598887</v>
@@ -46792,10 +46792,10 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.854920588390011</v>
+        <v>-4.753005283889558</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.014966927539257</v>
+        <v>1.055733049339438</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.191859592598887</v>
@@ -46815,10 +46815,10 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.848767882337227</v>
+        <v>-4.746852577836774</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.018090358352029</v>
+        <v>1.05885648015221</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1857068865461027</v>
@@ -46838,10 +46838,10 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.865577180487729</v>
+        <v>-4.763661875987276</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.010447115831939</v>
+        <v>1.05121323763212</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2025161846966044</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.803279181711607</v>
+        <v>-4.701363877211153</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.101701869139208</v>
+        <v>1.14246799093939</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2025161846966044</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.601488984046449</v>
+        <v>-4.499573679545995</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8909988205946695</v>
+        <v>0.9317649423948509</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.004497992527449979</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.541598302403855</v>
+        <v>-4.439682997903402</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.985245325573882</v>
+        <v>1.026011447374063</v>
       </c>
       <c r="F1972" t="n">
         <v>0.0553926891151435</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.63933884702883</v>
+        <v>-4.537423542528376</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.960776843839936</v>
+        <v>1.001542965640117</v>
       </c>
       <c r="F1973" t="n">
         <v>0.03950341098216331</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.815676607151759</v>
+        <v>-4.713761302651306</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8887777206154359</v>
+        <v>0.9295438424156173</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1368343491407661</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.744130284374882</v>
+        <v>-4.642214979874429</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9158878677661153</v>
+        <v>0.9566539895662967</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1368343491407661</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.699757152736313</v>
+        <v>-4.59784184823586</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.933499987856979</v>
+        <v>0.9742661096571603</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.09246121750219749</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.691803182441541</v>
+        <v>-4.589887877941088</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9366815759748879</v>
+        <v>0.977447697775069</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.09246121750219749</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.644147451880485</v>
+        <v>-4.542232147380032</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9621256252271149</v>
+        <v>1.002891747027296</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.04480548694114184</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.516463142086189</v>
+        <v>-4.414547837585736</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.018091722519558</v>
+        <v>1.058857844319739</v>
       </c>
       <c r="F1979" t="n">
         <v>0.08287882285315462</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.577129732488578</v>
+        <v>-4.475214427988125</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9805797588344745</v>
+        <v>1.021345880634656</v>
       </c>
       <c r="F1980" t="n">
         <v>0.001180506134620951</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.53229133088018</v>
+        <v>-4.430376026379727</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.002612822088462</v>
+        <v>1.043378943888644</v>
       </c>
       <c r="F1981" t="n">
         <v>0.005723939079490425</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.633049966637178</v>
+        <v>-4.531134662136725</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9664703074167413</v>
+        <v>1.007236429216923</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.083101629647515</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.588847129551278</v>
+        <v>-4.486931825050824</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9900310447789387</v>
+        <v>1.03079716657912</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.03889879256161455</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.62582615721472</v>
+        <v>-4.523910852714267</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.973649434182809</v>
+        <v>1.01441555598299</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.001924890770284016</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.645884236079561</v>
+        <v>-4.543968931579108</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.016873967819913</v>
+        <v>1.057640089620094</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.001924890770284016</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.605953562901671</v>
+        <v>-4.504038258401217</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.031286941685322</v>
+        <v>1.072053063485503</v>
       </c>
       <c r="F1986" t="n">
         <v>0.03800578240760633</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.565483215338966</v>
+        <v>-4.463567910838512</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.042423308948674</v>
+        <v>1.083189430748855</v>
       </c>
       <c r="F1987" t="n">
         <v>0.07847612997031128</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.50025903421176</v>
+        <v>-4.398343729711307</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.085700385492261</v>
+        <v>1.126466507292442</v>
       </c>
       <c r="F1988" t="n">
         <v>0.1437003110975169</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.550753324568817</v>
+        <v>-4.448838020068363</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.061463641648719</v>
+        <v>1.1022297634489</v>
       </c>
       <c r="F1989" t="n">
         <v>0.09867957397144267</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.570864980603525</v>
+        <v>-4.468949676103072</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.054675771566076</v>
+        <v>1.095441893366257</v>
       </c>
       <c r="F1990" t="n">
         <v>0.1097069189688619</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.668545559876171</v>
+        <v>-4.566630255375718</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.176161310878228</v>
+        <v>1.216927432678409</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.0009962763713269318</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.644753991270028</v>
+        <v>-4.542838686769575</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.305790847538502</v>
+        <v>1.346556969338684</v>
       </c>
       <c r="F1992" t="n">
         <v>0.02279529223481536</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.681508409831751</v>
+        <v>-4.579593105331297</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.282797056127672</v>
+        <v>1.323563177927854</v>
       </c>
       <c r="F1993" t="n">
         <v>0.02279529223481536</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.677174106774703</v>
+        <v>-4.57525880227425</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.282723972934271</v>
+        <v>1.323490094734452</v>
       </c>
       <c r="F1994" t="n">
         <v>0.1744453955540193</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.66828164538142</v>
+        <v>-4.566366340880966</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.303835363218375</v>
+        <v>1.344601485018557</v>
       </c>
       <c r="F1995" t="n">
         <v>0.1744453955540193</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.836757762351297</v>
+        <v>-4.734842457850844</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.228299963835009</v>
+        <v>1.26906608563519</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1464975598374385</v>
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.431236795039063</v>
+        <v>3.7486156716724</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.829366005115927</v>
+        <v>-4.584355776254793</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.301669328186</v>
+        <v>1.399673419730454</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.150399038524355</v>
+        <v>0.107849189680009</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.324011577660732</v>
+        <v>3.298481668354124</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>16.6%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.1%</t>
+          <t>105.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>85.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.4%</t>
+          <t>452.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-620.0%</t>
+          <t>-634.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-236.3%</t>
+          <t>-242.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-20.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-13.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.2%</t>
+          <t>-209.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-06-16</t>
+          <t>2024-06-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-116.2%</t>
+          <t>-118.5%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1997"/>
+  <dimension ref="A1:G1998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.721563258226239</v>
+        <v>-4.72384656375074</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8334934043739262</v>
+        <v>0.8325800821641258</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1037690524253604</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.74117406991342</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.683179595668088</v>
+        <v>-4.685462901192589</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8462663107395554</v>
+        <v>0.8453529885297548</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.06538538986720921</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.75114719753248</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.506063265632922</v>
+        <v>-4.508346571157423</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9138418715989236</v>
+        <v>0.9129285493891233</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.06538538986720921</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793897</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.551155510466468</v>
+        <v>-4.553438815990969</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8964883654274185</v>
+        <v>0.8955750432176179</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.127281433036599</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.3717800892277</v>
+        <v>-4.374063394752201</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9620255092293399</v>
+        <v>0.9611121870195394</v>
       </c>
       <c r="F1957" t="n">
         <v>0.02949532513411968</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982226</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.416794302748307</v>
+        <v>-4.419077608272807</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.924827279152687</v>
+        <v>0.9239139569428869</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.0008535701804849305</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.683798813020742</v>
+        <v>-4.686082118545242</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8237170373826588</v>
+        <v>0.8228037151728587</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1952166082234335</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.784996594457914</v>
+        <v>-4.787279899982415</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7824418467042911</v>
+        <v>0.781528524494491</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2636254217687527</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.752521008287142</v>
+        <v>-4.754804313811642</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7930320427269166</v>
+        <v>0.7921187205171165</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2636254217687527</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.733482880579845</v>
+        <v>-4.735766186104345</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7971720130180806</v>
+        <v>0.7962586908082805</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3218090330999472</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131247</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.764609511730463</v>
+        <v>-4.766892817254964</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9623032294965137</v>
+        <v>0.9613899072867136</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3218090330999472</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.778476273064381</v>
+        <v>-4.780759578588881</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9575898539490801</v>
+        <v>0.95667653173928</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3596669498337702</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.798733571593339</v>
+        <v>-4.801016877117839</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9554954649344229</v>
+        <v>0.9545821427246228</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3596669498337702</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.650990601358337</v>
+        <v>-4.653273906882837</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.093745300820446</v>
+        <v>1.092831978610646</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.191859592598887</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.753005283889558</v>
+        <v>-4.755288589414058</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.055733049339438</v>
+        <v>1.054819727129638</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.191859592598887</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.746852577836774</v>
+        <v>-4.749135883361274</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.05885648015221</v>
+        <v>1.05794315794241</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1857068865461027</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.763661875987276</v>
+        <v>-4.765945181511776</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.05121323763212</v>
+        <v>1.05029991542232</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2025161846966044</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.701363877211153</v>
+        <v>-4.703647182735653</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.14246799093939</v>
+        <v>1.14155466872959</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2025161846966044</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.499573679545995</v>
+        <v>-4.501856985070495</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9317649423948509</v>
+        <v>0.9308516201850507</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.004497992527449979</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.439682997903402</v>
+        <v>-4.441966303427902</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.026011447374063</v>
+        <v>1.025098125164263</v>
       </c>
       <c r="F1972" t="n">
         <v>0.0553926891151435</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.537423542528376</v>
+        <v>-4.539706848052877</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.001542965640117</v>
+        <v>1.000629643430317</v>
       </c>
       <c r="F1973" t="n">
         <v>0.03950341098216331</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.713761302651306</v>
+        <v>-4.716044608175806</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9295438424156173</v>
+        <v>0.9286305202058172</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1368343491407661</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.642214979874429</v>
+        <v>-4.644498285398929</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9566539895662967</v>
+        <v>0.9557406673564965</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1368343491407661</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.59784184823586</v>
+        <v>-4.60012515376036</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9742661096571603</v>
+        <v>0.9733527874473602</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.09246121750219749</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.589887877941088</v>
+        <v>-4.592171183465588</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.977447697775069</v>
+        <v>0.9765343755652691</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.09246121750219749</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.542232147380032</v>
+        <v>-4.544515452904532</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.002891747027296</v>
+        <v>1.001978424817496</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.04480548694114184</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.414547837585736</v>
+        <v>-4.416831143110236</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.058857844319739</v>
+        <v>1.057944522109939</v>
       </c>
       <c r="F1979" t="n">
         <v>0.08287882285315462</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.475214427988125</v>
+        <v>-4.477497733512625</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.021345880634656</v>
+        <v>1.020432558424856</v>
       </c>
       <c r="F1980" t="n">
         <v>0.001180506134620951</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.430376026379727</v>
+        <v>-4.432659331904227</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.043378943888644</v>
+        <v>1.042465621678844</v>
       </c>
       <c r="F1981" t="n">
         <v>0.005723939079490425</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.531134662136725</v>
+        <v>-4.533417967661225</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.007236429216923</v>
+        <v>1.006323107007123</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.083101629647515</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.486931825050824</v>
+        <v>-4.489215130575325</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.03079716657912</v>
+        <v>1.02988384436932</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.03889879256161455</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.523910852714267</v>
+        <v>-4.526194158238767</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.01441555598299</v>
+        <v>1.01350223377319</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.001924890770284016</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.543968931579108</v>
+        <v>-4.546252237103608</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.057640089620094</v>
+        <v>1.056726767410294</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.001924890770284016</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.504038258401217</v>
+        <v>-4.506321563925717</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.072053063485503</v>
+        <v>1.071139741275703</v>
       </c>
       <c r="F1986" t="n">
         <v>0.03800578240760633</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.463567910838512</v>
+        <v>-4.465851216363013</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.083189430748855</v>
+        <v>1.082276108539055</v>
       </c>
       <c r="F1987" t="n">
         <v>0.07847612997031128</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.398343729711307</v>
+        <v>-4.400627035235807</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.126466507292442</v>
+        <v>1.125553185082642</v>
       </c>
       <c r="F1988" t="n">
         <v>0.1437003110975169</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.448838020068363</v>
+        <v>-4.451121325592863</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.1022297634489</v>
+        <v>1.1013164412391</v>
       </c>
       <c r="F1989" t="n">
         <v>0.09867957397144267</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.468949676103072</v>
+        <v>-4.471232981627572</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.095441893366257</v>
+        <v>1.094528571156457</v>
       </c>
       <c r="F1990" t="n">
         <v>0.1097069189688619</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.566630255375718</v>
+        <v>-4.568913560900218</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.216927432678409</v>
+        <v>1.216014110468609</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.0009962763713269318</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.542838686769575</v>
+        <v>-4.545121992294075</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.346556969338684</v>
+        <v>1.345643647128884</v>
       </c>
       <c r="F1992" t="n">
         <v>0.02279529223481536</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.579593105331297</v>
+        <v>-4.581876410855798</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.323563177927854</v>
+        <v>1.322649855718053</v>
       </c>
       <c r="F1993" t="n">
         <v>0.02279529223481536</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.57525880227425</v>
+        <v>-4.57754210779875</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.323490094734452</v>
+        <v>1.322576772524652</v>
       </c>
       <c r="F1994" t="n">
         <v>0.1744453955540193</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.566366340880966</v>
+        <v>-4.568649646405467</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.344601485018557</v>
+        <v>1.343688162808757</v>
       </c>
       <c r="F1995" t="n">
         <v>0.1744453955540193</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.734842457850844</v>
+        <v>-4.737125763375344</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.26906608563519</v>
+        <v>1.26815276342539</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1464975598374385</v>
@@ -47476,22 +47476,45 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.7486156716724</v>
+        <v>3.79560310053997</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.584355776254793</v>
+        <v>-4.729734006139974</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.399673419730454</v>
+        <v>1.341522127776382</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.107849189680009</v>
+        <v>0.150399038524355</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.298481668354124</v>
+        <v>3.324011577660732</v>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" s="2" t="n">
+        <v>45460</v>
+      </c>
+      <c r="B1998" t="n">
+        <v>3.748669604118842</v>
+      </c>
+      <c r="C1998" t="n">
+        <v>3.281850693483401</v>
+      </c>
+      <c r="D1998" t="n">
+        <v>-4.729734006139974</v>
+      </c>
+      <c r="E1998" t="n">
+        <v>1.341522127776382</v>
+      </c>
+      <c r="F1998" t="n">
+        <v>0.150399038524355</v>
+      </c>
+      <c r="G1998" t="n">
+        <v>3.274914490469769</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.9%</t>
+          <t>-77.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>106.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-50.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-73.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>87.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.0%</t>
+          <t>452.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-634.5%</t>
+          <t>-620.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-42.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-242.1%</t>
+          <t>-236.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.6%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-13.7%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.0%</t>
+          <t>-213.2%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611566</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.76461787988307</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074778</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242289</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.72384656375074</v>
+        <v>-4.721563258226239</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8325800821641258</v>
+        <v>0.8334934043739262</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1037690524253604</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.74117406991342</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.685462901192589</v>
+        <v>-4.683179595668088</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8453529885297548</v>
+        <v>0.8462663107395554</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.06538538986720921</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.75114719753248</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.508346571157423</v>
+        <v>-4.506063265632922</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9129285493891233</v>
+        <v>0.9138418715989236</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.06538538986720921</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793897</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.553438815990969</v>
+        <v>-4.551155510466468</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8955750432176179</v>
+        <v>0.8964883654274185</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.127281433036599</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.374063394752201</v>
+        <v>-4.3717800892277</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9611121870195394</v>
+        <v>0.9620255092293399</v>
       </c>
       <c r="F1957" t="n">
         <v>0.02949532513411968</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982226</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.419077608272807</v>
+        <v>-4.416794302748307</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9239139569428869</v>
+        <v>0.924827279152687</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.0008535701804849305</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.686082118545242</v>
+        <v>-4.683798813020742</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8228037151728587</v>
+        <v>0.8237170373826588</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1952166082234335</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760806</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.787279899982415</v>
+        <v>-4.784996594457914</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.781528524494491</v>
+        <v>0.7824418467042911</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2636254217687527</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.754804313811642</v>
+        <v>-4.752521008287142</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7921187205171165</v>
+        <v>0.7930320427269166</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2636254217687527</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.735766186104345</v>
+        <v>-4.733482880579845</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7962586908082805</v>
+        <v>0.7971720130180806</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3218090330999472</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131247</v>
+        <v>3.731064473131249</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.766892817254964</v>
+        <v>-4.764609511730463</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9613899072867136</v>
+        <v>0.9623032294965137</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3218090330999472</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.780759578588881</v>
+        <v>-4.778476273064381</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.95667653173928</v>
+        <v>0.9575898539490801</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3596669498337702</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.801016877117839</v>
+        <v>-4.798733571593339</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9545821427246228</v>
+        <v>0.9554954649344229</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3596669498337702</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519905</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.653273906882837</v>
+        <v>-4.650990601358337</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.092831978610646</v>
+        <v>1.093745300820446</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.191859592598887</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.755288589414058</v>
+        <v>-4.753005283889558</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.054819727129638</v>
+        <v>1.055733049339438</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.191859592598887</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394727</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.749135883361274</v>
+        <v>-4.746852577836774</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.05794315794241</v>
+        <v>1.05885648015221</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1857068865461027</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890608</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.765945181511776</v>
+        <v>-4.763661875987276</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.05029991542232</v>
+        <v>1.05121323763212</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2025161846966044</v>
@@ -46861,10 +46861,10 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.703647182735653</v>
+        <v>-4.701363877211153</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.14155466872959</v>
+        <v>1.14246799093939</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2025161846966044</v>
@@ -46884,10 +46884,10 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.501856985070495</v>
+        <v>-4.499573679545995</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9308516201850507</v>
+        <v>0.9317649423948509</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.004497992527449979</v>
@@ -46907,10 +46907,10 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.441966303427902</v>
+        <v>-4.439682997903402</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.025098125164263</v>
+        <v>1.026011447374063</v>
       </c>
       <c r="F1972" t="n">
         <v>0.0553926891151435</v>
@@ -46930,10 +46930,10 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.539706848052877</v>
+        <v>-4.537423542528376</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.000629643430317</v>
+        <v>1.001542965640117</v>
       </c>
       <c r="F1973" t="n">
         <v>0.03950341098216331</v>
@@ -46953,10 +46953,10 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.716044608175806</v>
+        <v>-4.713761302651306</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9286305202058172</v>
+        <v>0.9295438424156173</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1368343491407661</v>
@@ -46976,10 +46976,10 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.644498285398929</v>
+        <v>-4.642214979874429</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9557406673564965</v>
+        <v>0.9566539895662967</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1368343491407661</v>
@@ -46999,10 +46999,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.60012515376036</v>
+        <v>-4.59784184823586</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9733527874473602</v>
+        <v>0.9742661096571603</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.09246121750219749</v>
@@ -47022,10 +47022,10 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.592171183465588</v>
+        <v>-4.589887877941088</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9765343755652691</v>
+        <v>0.977447697775069</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.09246121750219749</v>
@@ -47045,10 +47045,10 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.544515452904532</v>
+        <v>-4.542232147380032</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.001978424817496</v>
+        <v>1.002891747027296</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.04480548694114184</v>
@@ -47068,10 +47068,10 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.416831143110236</v>
+        <v>-4.414547837585736</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.057944522109939</v>
+        <v>1.058857844319739</v>
       </c>
       <c r="F1979" t="n">
         <v>0.08287882285315462</v>
@@ -47091,10 +47091,10 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.477497733512625</v>
+        <v>-4.475214427988125</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.020432558424856</v>
+        <v>1.021345880634656</v>
       </c>
       <c r="F1980" t="n">
         <v>0.001180506134620951</v>
@@ -47114,10 +47114,10 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.432659331904227</v>
+        <v>-4.430376026379727</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.042465621678844</v>
+        <v>1.043378943888644</v>
       </c>
       <c r="F1981" t="n">
         <v>0.005723939079490425</v>
@@ -47137,10 +47137,10 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.533417967661225</v>
+        <v>-4.531134662136725</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.006323107007123</v>
+        <v>1.007236429216923</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.083101629647515</v>
@@ -47160,10 +47160,10 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.489215130575325</v>
+        <v>-4.486931825050824</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.02988384436932</v>
+        <v>1.03079716657912</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.03889879256161455</v>
@@ -47183,10 +47183,10 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.526194158238767</v>
+        <v>-4.523910852714267</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.01350223377319</v>
+        <v>1.01441555598299</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.001924890770284016</v>
@@ -47206,10 +47206,10 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.546252237103608</v>
+        <v>-4.543968931579108</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.056726767410294</v>
+        <v>1.057640089620094</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.001924890770284016</v>
@@ -47229,10 +47229,10 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.506321563925717</v>
+        <v>-4.504038258401217</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.071139741275703</v>
+        <v>1.072053063485503</v>
       </c>
       <c r="F1986" t="n">
         <v>0.03800578240760633</v>
@@ -47252,10 +47252,10 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.465851216363013</v>
+        <v>-4.463567910838512</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.082276108539055</v>
+        <v>1.083189430748855</v>
       </c>
       <c r="F1987" t="n">
         <v>0.07847612997031128</v>
@@ -47275,10 +47275,10 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.400627035235807</v>
+        <v>-4.398343729711307</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.125553185082642</v>
+        <v>1.126466507292442</v>
       </c>
       <c r="F1988" t="n">
         <v>0.1437003110975169</v>
@@ -47298,10 +47298,10 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.451121325592863</v>
+        <v>-4.448838020068363</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.1013164412391</v>
+        <v>1.1022297634489</v>
       </c>
       <c r="F1989" t="n">
         <v>0.09867957397144267</v>
@@ -47321,10 +47321,10 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.471232981627572</v>
+        <v>-4.468949676103072</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.094528571156457</v>
+        <v>1.095441893366257</v>
       </c>
       <c r="F1990" t="n">
         <v>0.1097069189688619</v>
@@ -47344,10 +47344,10 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.568913560900218</v>
+        <v>-4.566630255375718</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.216014110468609</v>
+        <v>1.216927432678409</v>
       </c>
       <c r="F1991" t="n">
         <v>-0.0009962763713269318</v>
@@ -47367,10 +47367,10 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.545121992294075</v>
+        <v>-4.542838686769575</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.345643647128884</v>
+        <v>1.346556969338684</v>
       </c>
       <c r="F1992" t="n">
         <v>0.02279529223481536</v>
@@ -47390,10 +47390,10 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.581876410855798</v>
+        <v>-4.579593105331297</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.322649855718053</v>
+        <v>1.323563177927854</v>
       </c>
       <c r="F1993" t="n">
         <v>0.02279529223481536</v>
@@ -47413,10 +47413,10 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.57754210779875</v>
+        <v>-4.57525880227425</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.322576772524652</v>
+        <v>1.323490094734452</v>
       </c>
       <c r="F1994" t="n">
         <v>0.1744453955540193</v>
@@ -47436,10 +47436,10 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.568649646405467</v>
+        <v>-4.566366340880966</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.343688162808757</v>
+        <v>1.344601485018557</v>
       </c>
       <c r="F1995" t="n">
         <v>0.1744453955540193</v>
@@ -47459,10 +47459,10 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.737125763375344</v>
+        <v>-4.734842457850844</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.26815276342539</v>
+        <v>1.26906608563519</v>
       </c>
       <c r="F1996" t="n">
         <v>0.1464975598374385</v>
@@ -47482,16 +47482,16 @@
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.729734006139974</v>
+        <v>-4.584355776254793</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.341522127776382</v>
+        <v>1.399673419730454</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.150399038524355</v>
+        <v>0.107849189680009</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.324011577660732</v>
+        <v>3.298481668354124</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,19 +47499,19 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.748669604118842</v>
+        <v>3.748669604118841</v>
       </c>
       <c r="C1998" t="n">
         <v>3.281850693483401</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.729734006139974</v>
+        <v>-4.584355776254793</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.341522127776382</v>
+        <v>1.399673419730454</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.150399038524355</v>
+        <v>0.107849189680009</v>
       </c>
       <c r="G1998" t="n">
         <v>3.274914490469769</v>

--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>50.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -864,12 +864,12 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>16.6%</t>
+          <t>11.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.3%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.1%</t>
+          <t>106.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.3%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.4%</t>
+          <t>452.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-620.0%</t>
+          <t>-627.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.7%</t>
+          <t>-42.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-236.3%</t>
+          <t>-241.1%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.2%</t>
+          <t>-20.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.4%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-190.2%</t>
+          <t>-195.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-213.2%</t>
+          <t>-210.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-118.5%</t>
+          <t>-123.8%</t>
         </is>
       </c>
     </row>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632778</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461787988307</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074778</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242289</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367681</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
@@ -46470,10 +46470,10 @@
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.721563258226239</v>
+        <v>-4.823478562726693</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8334934043739262</v>
+        <v>0.7927272825737446</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1037690524253604</v>
@@ -46493,10 +46493,10 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.683179595668088</v>
+        <v>-4.785094900168542</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8462663107395554</v>
+        <v>0.8055001889393736</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.06538538986720921</v>
@@ -46516,10 +46516,10 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.506063265632922</v>
+        <v>-4.607978570133376</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9138418715989236</v>
+        <v>0.873075749798742</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.06538538986720921</v>
@@ -46539,10 +46539,10 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.551155510466468</v>
+        <v>-4.653070814966922</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8964883654274185</v>
+        <v>0.8557222436272367</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.127281433036599</v>
@@ -46562,10 +46562,10 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.3717800892277</v>
+        <v>-4.473695393728154</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9620255092293399</v>
+        <v>0.9212593874291581</v>
       </c>
       <c r="F1957" t="n">
         <v>0.02949532513411968</v>
@@ -46585,10 +46585,10 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.416794302748307</v>
+        <v>-4.51870960724876</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.924827279152687</v>
+        <v>0.8840611573525057</v>
       </c>
       <c r="F1958" t="n">
         <v>-0.0008535701804849305</v>
@@ -46608,10 +46608,10 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.683798813020742</v>
+        <v>-4.785714117521195</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8237170373826588</v>
+        <v>0.7829509155824774</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1952166082234335</v>
@@ -46631,10 +46631,10 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.784996594457914</v>
+        <v>-4.886911898958368</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7824418467042911</v>
+        <v>0.7416757249041097</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2636254217687527</v>
@@ -46654,10 +46654,10 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.752521008287142</v>
+        <v>-4.854436312787596</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7930320427269166</v>
+        <v>0.7522659209267353</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2636254217687527</v>
@@ -46677,10 +46677,10 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.733482880579845</v>
+        <v>-4.835398185080298</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7971720130180806</v>
+        <v>0.7564058912178993</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3218090330999472</v>
@@ -46700,10 +46700,10 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.764609511730463</v>
+        <v>-4.866524816230917</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9623032294965137</v>
+        <v>0.9215371076963323</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3218090330999472</v>
@@ -46723,10 +46723,10 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.778476273064381</v>
+        <v>-4.880391577564835</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9575898539490801</v>
+        <v>0.9168237321488988</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.3596669498337702</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.798733571593339</v>
+        <v>-4.900648876093793</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9554954649344229</v>
+        <v>0.9147293431342416</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.3596669498337702</v>
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.954497965677528</v>
+        <v>2.937163225079544</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.650990601358337</v>
+        <v>-4.75290590585879</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.093745300820446</v>
+        <v>1.035644438422281</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.191859592598887</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.839382210118196</v>
+        <v>2.822047469520212</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.957291587209009</v>
+        <v>2.939956846611025</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.753005283889558</v>
+        <v>-4.854920588390011</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.055733049339438</v>
+        <v>0.9976321869412732</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.191859592598887</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.842175831649677</v>
+        <v>2.824841091051693</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394727</v>
+        <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.957953935600667</v>
+        <v>2.940619195002684</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.746852577836774</v>
+        <v>-4.848767882337227</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.05885648015221</v>
+        <v>1.000755617754045</v>
       </c>
       <c r="F1968" t="n">
         <v>-0.1857068865461027</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.846529803673006</v>
+        <v>2.829195063075022</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.79823979489061</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.957034412340778</v>
+        <v>2.939699671742794</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.763661875987276</v>
+        <v>-4.865577180487729</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.05121323763212</v>
+        <v>0.9931123752339548</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.2025161846966044</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.835524701522815</v>
+        <v>2.818189960924832</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.023369966137599</v>
+        <v>3.006035225539615</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.701363877211153</v>
+        <v>-4.803279181711607</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.14246799093939</v>
+        <v>1.084367128541225</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.2025161846966044</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.901860255319636</v>
+        <v>2.884525514721652</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992189</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.731950838526997</v>
+        <v>2.714616097929013</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.499573679545995</v>
+        <v>-4.601488984046449</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9317649423948509</v>
+        <v>0.8736640799966857</v>
       </c>
       <c r="F1971" t="n">
         <v>-0.004497992527449979</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.729252043010527</v>
+        <v>2.711917302412543</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852422</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.802241070849172</v>
+        <v>2.784906330251188</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.439682997903402</v>
+        <v>-4.541598302403855</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.026011447374063</v>
+        <v>0.9679105849758982</v>
       </c>
       <c r="F1972" t="n">
         <v>0.0553926891151435</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.835476684318258</v>
+        <v>2.818141943720275</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.816868806965215</v>
+        <v>2.799534066367232</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.537423542528376</v>
+        <v>-4.63933884702883</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.001542965640117</v>
+        <v>0.9434421032419522</v>
       </c>
       <c r="F1973" t="n">
         <v>0.03950341098216331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.840570853554514</v>
+        <v>2.82323611295653</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.815404787789887</v>
+        <v>2.798070047191903</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.713761302651306</v>
+        <v>-4.815676607151759</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9295438424156173</v>
+        <v>0.8714429800174521</v>
       </c>
       <c r="F1974" t="n">
         <v>-0.1368343491407661</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.733304178305428</v>
+        <v>2.715969437707444</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.813896405829816</v>
+        <v>2.796561665231832</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.642214979874429</v>
+        <v>-4.744130284374882</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9566539895662967</v>
+        <v>0.8985531271681315</v>
       </c>
       <c r="F1975" t="n">
         <v>-0.1368343491407661</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.731795796345356</v>
+        <v>2.714461055747373</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024961</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.813759273265252</v>
+        <v>2.796424532667268</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.59784184823586</v>
+        <v>-4.699757152736313</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9742661096571603</v>
+        <v>0.9161652472589952</v>
       </c>
       <c r="F1976" t="n">
         <v>-0.09246121750219749</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.758282542763934</v>
+        <v>2.74094780216595</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863222</v>
+        <v>3.821591150863224</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.813759273265252</v>
+        <v>2.796424532667268</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.589887877941088</v>
+        <v>-4.691803182441541</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.977447697775069</v>
+        <v>0.9193468353769041</v>
       </c>
       <c r="F1977" t="n">
         <v>-0.09246121750219749</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.758282542763934</v>
+        <v>2.74094780216595</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947581</v>
+        <v>3.833040181947583</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.820141030293057</v>
+        <v>2.802806289695073</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.542232147380032</v>
+        <v>-4.644147451880485</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.002891747027296</v>
+        <v>0.9447908846291311</v>
       </c>
       <c r="F1978" t="n">
         <v>-0.04480548694114184</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.793257738128372</v>
+        <v>2.775922997530388</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326874</v>
+        <v>3.822707244326875</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.825033403667781</v>
+        <v>2.807698663069798</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.414547837585736</v>
+        <v>-4.516463142086189</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.058857844319739</v>
+        <v>1.000756981921574</v>
       </c>
       <c r="F1979" t="n">
         <v>0.08287882285315462</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.874760697379674</v>
+        <v>2.85742595678169</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314549</v>
+        <v>3.828837911314551</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.811788076143654</v>
+        <v>2.79445333554567</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.475214427988125</v>
+        <v>-4.577129732488578</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.021345880634656</v>
+        <v>0.9632450182364907</v>
       </c>
       <c r="F1980" t="n">
         <v>0.001180506134620951</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.812496379824426</v>
+        <v>2.795161639226443</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690025</v>
+        <v>3.816866067690027</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.815885778754282</v>
+        <v>2.798551038156298</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.430376026379727</v>
+        <v>-4.53229133088018</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.043378943888644</v>
+        <v>0.9852780814904787</v>
       </c>
       <c r="F1981" t="n">
         <v>0.005723939079490425</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.819320142201977</v>
+        <v>2.801985401603993</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674309</v>
+        <v>3.817961388674311</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.82004671838536</v>
+        <v>2.802711977787376</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.531134662136725</v>
+        <v>-4.633049966637178</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.007236429216923</v>
+        <v>0.9491355668187575</v>
       </c>
       <c r="F1982" t="n">
         <v>-0.083101629647515</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.770185740596852</v>
+        <v>2.752850999998868</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163218</v>
+        <v>3.82671377916322</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.825926320913197</v>
+        <v>2.808591580315213</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.486931825050824</v>
+        <v>-4.588847129551278</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.03079716657912</v>
+        <v>0.9726963041809549</v>
       </c>
       <c r="F1983" t="n">
         <v>-0.03889879256161455</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.802587045376229</v>
+        <v>2.785252304778245</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022903</v>
+        <v>3.838228663022905</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.824336321382445</v>
+        <v>2.807001580784461</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.523910852714267</v>
+        <v>-4.62582615721472</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.01441555598299</v>
+        <v>0.9563146935848252</v>
       </c>
       <c r="F1984" t="n">
         <v>-0.001924890770284016</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.823181386920275</v>
+        <v>2.805846646322291</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042137</v>
+        <v>3.863924114042139</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.875584086565484</v>
+        <v>2.858249345967501</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.543968931579108</v>
+        <v>-4.645884236079561</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.057640089620094</v>
+        <v>0.9995392272219288</v>
       </c>
       <c r="F1985" t="n">
         <v>-0.001924890770284016</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.874429152103315</v>
+        <v>2.857094411505331</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078281</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.874024791159738</v>
+        <v>2.856690050561754</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.504038258401217</v>
+        <v>-4.580990714723294</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.072053063485503</v>
+        <v>1.023937340358689</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.03800578240760633</v>
+        <v>0.06296863058598312</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.896828260604302</v>
+        <v>2.894471228913344</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232397</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.868973019398008</v>
+        <v>2.851638278800024</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.463567910838512</v>
+        <v>-4.540520367160589</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.083189430748855</v>
+        <v>1.035073707622041</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.07847612997031128</v>
+        <v>0.1034389781486881</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.916058697380195</v>
+        <v>2.913701665689237</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162109</v>
+        <v>3.842576394162112</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.886160423490713</v>
+        <v>2.868825682892729</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.398343729711307</v>
+        <v>-4.475296186033384</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.126466507292442</v>
+        <v>1.078350784165628</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1437003110975169</v>
+        <v>0.1686631592758937</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.972380610149223</v>
+        <v>2.970023578458265</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639815</v>
+        <v>3.840090220639818</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.882121395789993</v>
+        <v>2.864786655192009</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.448838020068363</v>
+        <v>-4.52579047639044</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.1022297634489</v>
+        <v>1.054114040322086</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.09867957397144267</v>
+        <v>0.1236424221498195</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.941329140172859</v>
+        <v>2.938972108481901</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749918</v>
+        <v>3.84519884274992</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.883378188121233</v>
+        <v>2.866043447523249</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.468949676103072</v>
+        <v>-4.545902132425148</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.095441893366257</v>
+        <v>1.047326170239443</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1097069189688619</v>
+        <v>0.1346697671472387</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.949202339502551</v>
+        <v>2.946845307811593</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393543</v>
+        <v>3.828690479393545</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.043935959142444</v>
+        <v>3.02660121854446</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.566630255375718</v>
+        <v>-4.643582711697793</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.216927432678409</v>
+        <v>1.168811709551595</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.0009962763713269318</v>
+        <v>0.02396657180704986</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.043338193319648</v>
+        <v>3.04098116162869</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714881</v>
+        <v>3.813251854714883</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.164048868360261</v>
+        <v>3.146714127762277</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.542838686769575</v>
+        <v>-4.619791143091651</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.346556969338684</v>
+        <v>1.29844124621187</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.02279529223481536</v>
+        <v>0.04775814041319215</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.177726043701151</v>
+        <v>3.175369012010193</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175601</v>
+        <v>3.814259761756012</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.15575684437412</v>
+        <v>3.138422103776136</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.579593105331297</v>
+        <v>-4.656545561653373</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.323563177927854</v>
+        <v>1.275447454801039</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.02279529223481536</v>
+        <v>0.04775814041319215</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.169434019715009</v>
+        <v>3.167076988024052</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654186</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.1539500399579</v>
+        <v>3.136615299359916</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.57525880227425</v>
+        <v>-4.652211258596325</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.323490094734452</v>
+        <v>1.275374371607638</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1744453955540193</v>
+        <v>0.1994082437323961</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.258617277290312</v>
+        <v>3.256260245599354</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717115</v>
+        <v>3.796293177717117</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.171504445684691</v>
+        <v>3.154169705086707</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.566366340880966</v>
+        <v>-4.643318797203042</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.344601485018557</v>
+        <v>1.296485761891743</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1744453955540193</v>
+        <v>0.1994082437323961</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.276171683017103</v>
+        <v>3.273814651326145</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702625</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.163359493089275</v>
+        <v>3.146024752491291</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.734842457850844</v>
+        <v>-4.811794914172919</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.26906608563519</v>
+        <v>1.220950362508376</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1464975598374385</v>
+        <v>0.1714604080158153</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.251258028991738</v>
+        <v>3.248900997300781</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79560310053997</v>
+        <v>3.795603100539971</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.233772154546119</v>
+        <v>3.216437413948135</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.584355776254793</v>
+        <v>-4.661308232576869</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.399673419730454</v>
+        <v>1.35155769660364</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.107849189680009</v>
+        <v>0.1328120378583857</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.298481668354124</v>
+        <v>3.296124636663166</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.748669604118841</v>
+        <v>3.78415660239736</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.281850693483401</v>
+        <v>3.229547303820981</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.584355776254793</v>
+        <v>-4.661308232576869</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.399673419730454</v>
+        <v>1.35155769660364</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.107849189680009</v>
+        <v>0.1328120378583857</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.274914490469769</v>
+        <v>3.222611100807348</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>68.7%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>21.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.7%</t>
+          <t>-77.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.2%</t>
+          <t>104.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.4%</t>
+          <t>122.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>85.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-683.2%</t>
+          <t>-665.3%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.8%</t>
+          <t>-48.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.8%</t>
+          <t>453.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-627.7%</t>
+          <t>-625.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-273.7%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-40.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.9%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-241.1%</t>
+          <t>-238.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-20.9%</t>
+          <t>-21.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,17 +1293,17 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-291.7%</t>
+          <t>-277.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-14.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>119.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-195.1%</t>
+          <t>-173.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.7%</t>
+          <t>-216.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.8%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-175.4%</t>
+          <t>-166.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.7%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-123.8%</t>
+          <t>-113.3%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.981509849727543</v>
+        <v>-4.802885748115715</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.131111169826019</v>
+        <v>1.202560810470751</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.683459177750642</v>
+        <v>-0.5403280785412382</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.713996027380399</v>
+        <v>2.799874686906041</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.216203843860096</v>
+        <v>-5.037579742248267</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.025518347175089</v>
+        <v>1.09696798781982</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6771229105213868</v>
+        <v>-0.533991811311983</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.706082562720043</v>
+        <v>2.791961222245685</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.551866491090548</v>
+        <v>-5.37324238947872</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8898338799388732</v>
+        <v>0.9612835205836046</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6771229105213868</v>
+        <v>-0.533991811311983</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.704663154376008</v>
+        <v>2.79054181390165</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309422</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.915492735990862</v>
+        <v>-5.736868634379033</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7508709422129893</v>
+        <v>0.8223205828577207</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7753445473885127</v>
+        <v>-0.6322134481791089</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.652217732489974</v>
+        <v>2.738096392015616</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.280620118629608</v>
+        <v>-6.10199601701778</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.604074504163322</v>
+        <v>0.6755241448080533</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.071655331687525</v>
+        <v>-0.9285242324781213</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.473685776916398</v>
+        <v>2.55956443644204</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.30081581833052</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.689208895810287</v>
+        <v>-6.510584794198458</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4394005373058096</v>
+        <v>0.510850177950541</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.480244108868204</v>
+        <v>-1.3371130096588</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.22729405462275</v>
+        <v>2.313172714148392</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191735</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.96578499612612</v>
+        <v>-6.78716089451429</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3239555296509371</v>
+        <v>0.3954051702956689</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.480244108868204</v>
+        <v>-1.3371130096588</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.22247948709421</v>
+        <v>2.308358146619853</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108636</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.382176870413117</v>
+        <v>-7.203552768801288</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1553928305450154</v>
+        <v>0.2268424711897472</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.480244108868204</v>
+        <v>-1.3371130096588</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.220473537703088</v>
+        <v>2.30635219722873</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097819</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.652942959505762</v>
+        <v>-7.474318857893933</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0573450855766362</v>
+        <v>0.128794726221368</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.480244108868204</v>
+        <v>-1.3371130096588</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.230732228371767</v>
+        <v>2.316610887897409</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094114</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.998817781490571</v>
+        <v>-7.820193679878741</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08490527807159198</v>
+        <v>-0.01345563742686018</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.480244108868204</v>
+        <v>-1.3371130096588</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.226831793517462</v>
+        <v>2.312710453043104</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199281</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.162397659674955</v>
+        <v>-7.983773558063126</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1519323092903444</v>
+        <v>-0.08048266864561304</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.480244108868204</v>
+        <v>-1.3371130096588</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.225236713572463</v>
+        <v>2.311115373098105</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.459059001485153</v>
+        <v>-8.280434899873324</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2668178700852155</v>
+        <v>-0.1953682294404842</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.548987244602082</v>
+        <v>-1.405856145392678</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.187769808061344</v>
+        <v>2.273648467586986</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.645778709794456</v>
+        <v>-8.467154608182627</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3455320579433399</v>
+        <v>-0.274082417298608</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.548987244602082</v>
+        <v>-1.405856145392678</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.183743503526941</v>
+        <v>2.269622163052583</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297744</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.028780098537087</v>
+        <v>-8.850155996925258</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4988347147619763</v>
+        <v>-0.4273850741172449</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.548987244602082</v>
+        <v>-1.405856145392678</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.183641402205357</v>
+        <v>2.269520061730999</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.210649889522122</v>
+        <v>-9.032025787910293</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5690111151845603</v>
+        <v>-0.4975614745398285</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.730857035587117</v>
+        <v>-1.587725936377713</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.077091043585766</v>
+        <v>2.162969703111408</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737164</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.570180212026123</v>
+        <v>-9.391556110414294</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.7074729408881106</v>
+        <v>-0.6360233002433788</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.730857035587117</v>
+        <v>-1.587725936377713</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.082441346883816</v>
+        <v>2.168320006409458</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.620529275480346</v>
+        <v>-9.441905173868516</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.7196965463126221</v>
+        <v>-0.6482469056678903</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.781206099041339</v>
+        <v>-1.638074999831935</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.06014792876846</v>
+        <v>2.146026588294103</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539458</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.718148552901742</v>
+        <v>-9.539524451289912</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7557025066594116</v>
+        <v>-0.6842528660146798</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.878825376462736</v>
+        <v>-1.735694277253332</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.004618112937391</v>
+        <v>2.090496772463033</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937495</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.865674640907384</v>
+        <v>-9.687050539295555</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.8118193855400966</v>
+        <v>-0.7403697448953648</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.02635146446838</v>
+        <v>-1.883220365258976</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.918996016455577</v>
+        <v>2.004874675981219</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141698</v>
+        <v>3.502790399141699</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.06993281623725</v>
+        <v>-9.891308714625419</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8880094585534</v>
+        <v>-0.8165598179086677</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.153990409082369</v>
+        <v>-2.010859309872965</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.847925846805826</v>
+        <v>1.933804506331469</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729888</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.14426579249741</v>
+        <v>-9.965641690885583</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.9132600945730291</v>
+        <v>-0.8418104539282978</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.298689933017041</v>
+        <v>-2.155558833807637</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.765588686929459</v>
+        <v>1.851467346455101</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49997173944063</v>
+        <v>3.499971739440632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.07079596082996</v>
+        <v>-9.892171859218134</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.868500460412629</v>
+        <v>-0.7970508197678967</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.225220101349593</v>
+        <v>-2.082089002140189</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.825042287423349</v>
+        <v>1.910920946948991</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608597</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.24592037821651</v>
+        <v>-10.06729627660468</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.9239950066197293</v>
+        <v>-0.8525453659749971</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.400344518736137</v>
+        <v>-2.257213419526733</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.734522857738939</v>
+        <v>1.820401517264582</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410269</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.480372472231</v>
+        <v>-10.30174837061917</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.024995009127121</v>
+        <v>-0.9535453684823891</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.400344518736137</v>
+        <v>-2.257213419526733</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.727303692837343</v>
+        <v>1.813182352362986</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764393</v>
+        <v>3.480692492764395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.58474720325744</v>
+        <v>-10.40612310164561</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.073417092311676</v>
+        <v>-1.001967451666944</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.504719249762582</v>
+        <v>-2.361588150553179</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.6580066634475</v>
+        <v>1.743885322973142</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390583</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.63753335885777</v>
+        <v>-10.45890925724594</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.09341576471325</v>
+        <v>-1.021966124068518</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.600394736344979</v>
+        <v>-2.457263637135576</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.601717161336618</v>
+        <v>1.68759582086226</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.76357015222606</v>
+        <v>-10.58494605061423</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.141136753431451</v>
+        <v>-1.069687112786719</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.575143113535237</v>
+        <v>-2.432012014325833</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.619561863651578</v>
+        <v>1.70544052317722</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367402532254</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.71155463825725</v>
+        <v>-10.53293053664542</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.116340212157525</v>
+        <v>-1.044890571512793</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.575143113535237</v>
+        <v>-2.432012014325833</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.623552199337979</v>
+        <v>1.709430858863621</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158918</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.85322647998137</v>
+        <v>-10.67460237836954</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.174484175745915</v>
+        <v>-1.103034535101183</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.575143113535237</v>
+        <v>-2.432012014325833</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.622076972439237</v>
+        <v>1.707955631964879</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.80363563555653</v>
+        <v>-10.6250115339447</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.139594427811109</v>
+        <v>-1.068144787166377</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.525552269110403</v>
+        <v>-2.382421169900999</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.66688488925901</v>
+        <v>1.752763548784652</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770577</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.79082824255176</v>
+        <v>-10.61220414093993</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.147522604255883</v>
+        <v>-1.07607296361115</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.574408044119304</v>
+        <v>-2.431276944909901</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.624520290606986</v>
+        <v>1.710398950132628</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68516138161528</v>
+        <v>3.685161381615282</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.56498308983235</v>
+        <v>-10.38635898822052</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.047605470131909</v>
+        <v>-0.9761558294871775</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.532481368532141</v>
+        <v>-2.389350269322737</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.659255368995493</v>
+        <v>1.745134028521135</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812099</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.44040443349475</v>
+        <v>-10.26178033188293</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9966348630408128</v>
+        <v>-0.9251852223960824</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.532481368532141</v>
+        <v>-2.389350269322737</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.660394513551552</v>
+        <v>1.746273173077194</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.49329972153904</v>
+        <v>-10.31467561992721</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.01515920409642</v>
+        <v>-0.943709563451689</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.527526022443694</v>
+        <v>-2.384394923234291</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.666001495366727</v>
+        <v>1.751880154892369</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.42116654625116</v>
+        <v>-10.24254244463933</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9805722297426316</v>
+        <v>-0.9091225890979002</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.527526022443694</v>
+        <v>-2.384394923234291</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.671735199605364</v>
+        <v>1.757613859131006</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955325</v>
+        <v>3.728577929955327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.34980015364151</v>
+        <v>-10.17117605202968</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9617629350926373</v>
+        <v>-0.8903132944479069</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.456159629834046</v>
+        <v>-2.313028530624643</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.704817772777287</v>
+        <v>1.79069643230293</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.747702660232411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.08596328643744</v>
+        <v>-9.907339184825615</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.8661116695239168</v>
+        <v>-0.7946620288791864</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.456159629834046</v>
+        <v>-2.313028530624643</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.69493429146438</v>
+        <v>1.780812950990022</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.818721485569045</v>
+        <v>-9.640097383957217</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.761049509675932</v>
+        <v>-0.6895998690312006</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.456159629834046</v>
+        <v>-2.313028530624643</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.693099730965006</v>
+        <v>1.778978390490648</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.720814446892554</v>
+        <v>-9.542190345280726</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.7221870091787963</v>
+        <v>-0.6507373685340654</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.38817387997349</v>
+        <v>-2.245042780764086</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.733590865907879</v>
+        <v>1.819469525433521</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.80082935409724</v>
+        <v>3.800829354097243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.696860905916596</v>
+        <v>-9.518236804304768</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.7119370866429198</v>
+        <v>-0.6404874459981884</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.364220338997532</v>
+        <v>-2.221089239788129</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.748631496638947</v>
+        <v>1.834510156164589</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.432800967593799</v>
+        <v>-9.254176865981972</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6195734274755531</v>
+        <v>-0.5481237868308222</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.100160400674736</v>
+        <v>-1.957029301465332</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.893807143470873</v>
+        <v>1.979685802996515</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.725721344088962</v>
+        <v>-8.547097242477134</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3395286117339191</v>
+        <v>-0.2680789710891878</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.100160400674736</v>
+        <v>-1.957029301465332</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.891020109810572</v>
+        <v>1.976898769336214</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.685537045722771</v>
+        <v>-8.506912944110944</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3231112684996016</v>
+        <v>-0.2516616278548702</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.059976102308545</v>
+        <v>-1.916845003099142</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.915474312718128</v>
+        <v>2.00135297224377</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.52213717478341</v>
+        <v>-8.343513073171582</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2583844989030997</v>
+        <v>-0.1869348582583688</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.896576231369183</v>
+        <v>-1.753445132159779</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.012881056502502</v>
+        <v>2.098759716028144</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291808</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.28865595255381</v>
+        <v>-8.110031850941983</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1570675811734077</v>
+        <v>-0.08561794052867677</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.663095009139584</v>
+        <v>-1.519963909930181</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.160894218678114</v>
+        <v>2.246772878203756</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.138989561546296</v>
+        <v>-7.960365459934468</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.100093235083361</v>
+        <v>-0.02864359443862963</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.570191517897048</v>
+        <v>-1.427060418687645</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.213744103110676</v>
+        <v>2.299622762636318</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390424</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.006714087915409</v>
+        <v>-7.828089986303581</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05181555888397948</v>
+        <v>0.01963408176075188</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.437916044266162</v>
+        <v>-1.294784945056758</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.288476874036235</v>
+        <v>2.374355533561877</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.816114413242256</v>
+        <v>-7.637490311630429</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02723937167291801</v>
+        <v>0.09868901231764937</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.247316369593009</v>
+        <v>-1.104185270383605</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.405651739527763</v>
+        <v>2.491530399053405</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.567114614558675</v>
+        <v>-7.388490512946848</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1397456323700093</v>
+        <v>0.2111952730147406</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.247316369593009</v>
+        <v>-1.104185270383605</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.418558080751422</v>
+        <v>2.504436740277064</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.67270460433178</v>
+        <v>-7.494080502719952</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.03046629313845095</v>
+        <v>0.04098334750628041</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.352906359366113</v>
+        <v>-1.20977526015671</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.227228157288341</v>
+        <v>2.313106816813983</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.691439506450377</v>
+        <v>-7.512815404838549</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01058408789119625</v>
+        <v>0.08203372853592761</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.358502369026245</v>
+        <v>-1.215371269816841</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.272414893369348</v>
+        <v>2.35829355289499</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710808</v>
+        <v>3.76033368671081</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.543499465042777</v>
+        <v>-7.36487536343095</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.05011881823393161</v>
+        <v>0.02133082241079975</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.338181453117687</v>
+        <v>-1.195050353908283</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.164728520226316</v>
+        <v>2.250607179751958</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.490529942788789</v>
+        <v>-7.311905841176961</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.03764499558581402</v>
+        <v>0.03380464505891734</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.285211930863698</v>
+        <v>-1.142080831654294</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.187796247325231</v>
+        <v>2.273674906850873</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098106</v>
+        <v>3.729969716098108</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.446981536018098</v>
+        <v>-7.268357434406271</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.027186244972631</v>
+        <v>0.04426339567210036</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.285211930863698</v>
+        <v>-1.142080831654294</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.180835635230137</v>
+        <v>2.26671429475578</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493417</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.20483314256424</v>
+        <v>-7.026209040952413</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.08413546679005535</v>
+        <v>0.1555851074347867</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.285211930863698</v>
+        <v>-1.142080831654294</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.195297989611281</v>
+        <v>2.281176649136923</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722813</v>
+        <v>3.828551486722815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.096574005441719</v>
+        <v>-6.917949903829891</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.121971242098259</v>
+        <v>0.1934208827429904</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.285211930863698</v>
+        <v>-1.142080831654294</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.189830110070476</v>
+        <v>2.275708769596118</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.973282870624588</v>
+        <v>-6.79465876901276</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1687857900356882</v>
+        <v>0.2402354306804195</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.161920796046568</v>
+        <v>-1.018789696837164</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.261302884971331</v>
+        <v>2.347181544496973</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919906</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.952133671721144</v>
+        <v>-6.773509570109317</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1849464478343905</v>
+        <v>0.2563960884791219</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.140771597143124</v>
+        <v>-0.9976404979337206</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.281693382550722</v>
+        <v>2.367572042076364</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.7083682297377</v>
+        <v>-6.529744128125873</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.278233332974819</v>
+        <v>0.3496829736195504</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.140771597143124</v>
+        <v>-0.9976404979337206</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.277474090897773</v>
+        <v>2.363352750423415</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.606605409460405</v>
+        <v>-6.427981307848578</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3210627750057529</v>
+        <v>0.3925124156504842</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.127552528750696</v>
+        <v>-0.9844214295412919</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287529845853246</v>
+        <v>2.373408505378888</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279182</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.356755015511331</v>
+        <v>-6.178130913899503</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4137450075690849</v>
+        <v>0.4851946482138163</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.127552528750696</v>
+        <v>-0.9844214295412919</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280271920836948</v>
+        <v>2.36615058036259</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011495</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.180862923043898</v>
+        <v>-6.002238821432071</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.487700968076707</v>
+        <v>0.559150608721438</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.127552528750696</v>
+        <v>-0.9844214295412919</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283871044357597</v>
+        <v>2.369749703883239</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.009416460021434</v>
+        <v>-5.830792358409608</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.569607059340246</v>
+        <v>0.6410566999849769</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9561060657282324</v>
+        <v>-0.8129749665188287</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.400066428225628</v>
+        <v>2.48594508775127</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.77376522263278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.935126894283095</v>
+        <v>-5.756502792671268</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5983433632518786</v>
+        <v>0.6697930038966096</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8818164999898932</v>
+        <v>-0.7386854007804895</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.443660645284929</v>
+        <v>2.529539304810571</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.871491152049161</v>
+        <v>-5.692867050437334</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6284924611997695</v>
+        <v>0.6999421018445009</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8181807577559587</v>
+        <v>-0.675049658546555</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.486536891679607</v>
+        <v>2.572415551205249</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.827728970743319</v>
+        <v>-5.649104869131492</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.627191592505902</v>
+        <v>0.6986412331506329</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8181807577559587</v>
+        <v>-0.675049658546555</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.467731150463402</v>
+        <v>2.553609809989045</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.587298473938459</v>
+        <v>-5.408674372326632</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7251068678527233</v>
+        <v>0.7965565084974546</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5777502609510984</v>
+        <v>-0.4346191617416947</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.613732525171196</v>
+        <v>2.699611184696838</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367681</v>
+        <v>3.821593509367684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.515055905767264</v>
+        <v>-5.336431804155437</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7579332089560213</v>
+        <v>0.8293828496007527</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5777502609510984</v>
+        <v>-0.4346191617416947</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.617661839006016</v>
+        <v>2.703540498531658</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.462057583485876</v>
+        <v>-5.28343348187405</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7798111217859165</v>
+        <v>0.8512607624306479</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5224140019491595</v>
+        <v>-0.3792829027397558</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.651542178324519</v>
+        <v>2.737420837850161</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502335</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.353252698006149</v>
+        <v>-5.174628596394323</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.820331147197801</v>
+        <v>0.8917807878425319</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5224140019491595</v>
+        <v>-0.3792829027397558</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.648540249544513</v>
+        <v>2.734418909070155</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675938</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.133231899969139</v>
+        <v>-4.954607798357312</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9099185034232193</v>
+        <v>0.9813681440679503</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3811941568811793</v>
+        <v>-0.2380630576717756</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.734851193595915</v>
+        <v>2.820729853121557</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539945</v>
+        <v>3.843274527539949</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.000364210905861</v>
+        <v>-4.821740109294034</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9789597618503536</v>
+        <v>1.050409402495085</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3811941568811793</v>
+        <v>-0.2380630576717756</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.750745376397739</v>
+        <v>2.836624035923381</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.880191127541362</v>
+        <v>-4.701567025929536</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.028174839636455</v>
+        <v>1.099624480281186</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2610210735166804</v>
+        <v>-0.1178899743072767</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.82399507085674</v>
+        <v>2.909873730382382</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576994</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.735518982441625</v>
+        <v>-4.556894880829798</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.09613180023779</v>
+        <v>1.167581440882521</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1163489284169429</v>
+        <v>0.02678217079246076</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.920886460478022</v>
+        <v>3.006765120003664</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.795393809799317</v>
+        <v>-4.616769708187491</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.058219360696139</v>
+        <v>1.12966900134087</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1762237557746351</v>
+        <v>-0.03309265656523136</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.870999055464833</v>
+        <v>2.956877714990475</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.708594312020309</v>
+        <v>-4.529970210408482</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.115339653130308</v>
+        <v>1.186789293775039</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1762237557746351</v>
+        <v>-0.03309265656523136</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.893399548787399</v>
+        <v>2.979278208313041</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.711064018482115</v>
+        <v>-4.532439916870288</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.114424171918998</v>
+        <v>1.185873812563729</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1786934622364412</v>
+        <v>-0.03556236302703752</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.891990126283727</v>
+        <v>2.977868785809369</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.779434204806125</v>
+        <v>-4.600810103194299</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.098083019864096</v>
+        <v>1.169532660508827</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1694177632002263</v>
+        <v>-0.02628666399082258</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.908562468180158</v>
+        <v>2.9944411277058</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508366</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.887972385722259</v>
+        <v>-4.709348284110432</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.045104456129534</v>
+        <v>1.116554096774265</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1694177632002263</v>
+        <v>-0.02628666399082258</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.898999176812049</v>
+        <v>2.984877836337692</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417702</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.918965545050964</v>
+        <v>-4.740341443439138</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8574167574384384</v>
+        <v>0.9288663980831693</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1694177632002263</v>
+        <v>-0.02628666399082258</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.723708741852436</v>
+        <v>2.809587401378078</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.743491285258496</v>
+        <v>-4.564867183646669</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9321736933472136</v>
+        <v>1.003623333991944</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1694177632002263</v>
+        <v>-0.02628666399082258</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.728275973844224</v>
+        <v>2.814154633369866</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.854427537899745</v>
+        <v>-4.675803436287918</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8635412210519211</v>
+        <v>0.934990861696652</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1694177632002263</v>
+        <v>-0.02628666399082258</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.704018002605431</v>
+        <v>2.789896662131073</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.77321029711129</v>
+        <v>3.773210297111292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.862709612044803</v>
+        <v>-4.684085510432976</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8633597766138033</v>
+        <v>0.9348094172585342</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1776998373452847</v>
+        <v>-0.03456873813588096</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.702180143338301</v>
+        <v>2.788058802863944</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264159</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.80285699284108</v>
+        <v>-4.624232891229253</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.8974732107274248</v>
+        <v>0.9689228513721559</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1776998373452847</v>
+        <v>-0.03456873813588096</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.712352529770434</v>
+        <v>2.798231189296076</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742295</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.716613529814702</v>
+        <v>-4.537989428202875</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9269168665118364</v>
+        <v>0.9983665071565673</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1776998373452847</v>
+        <v>-0.03456873813588096</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.707298800344294</v>
+        <v>2.793177459869936</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.761920349213682</v>
+        <v>-4.583296247601855</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9005699141967698</v>
+        <v>0.9720195548415009</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2185100003545155</v>
+        <v>-0.07537890114511175</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.674588477983281</v>
+        <v>2.760467137508924</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.790953453915983</v>
+        <v>-4.612329352304156</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8895085453489511</v>
+        <v>0.960958185993682</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2185100003545155</v>
+        <v>-0.07537890114511175</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.675140351016383</v>
+        <v>2.761019010542025</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.698142972465123</v>
+        <v>-4.519518870853297</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8559054298206605</v>
+        <v>0.9273550704653915</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1256995189036561</v>
+        <v>0.0174315803057476</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.660099331778264</v>
+        <v>2.745977991303906</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.742532441794551</v>
+        <v>-4.563908340182724</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8400231180134903</v>
+        <v>0.9114727586582214</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1700889882330838</v>
+        <v>-0.02695788902368007</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.635339126105208</v>
+        <v>2.72121778563085</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.629861223558301</v>
+        <v>-4.451237121946474</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.8801673138197135</v>
+        <v>0.9516169544644444</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.05741776999683357</v>
+        <v>0.08571332921257013</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.698017565558681</v>
+        <v>2.783896225084324</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.517484222375628</v>
+        <v>-4.338860120763801</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9306094101234499</v>
+        <v>1.002059050768181</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.05741776999683357</v>
+        <v>0.08571332921257013</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.703508861389349</v>
+        <v>2.789387520914991</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.54526462027698</v>
+        <v>-4.366640518665154</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9309944527314478</v>
+        <v>1.002444093376179</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.08519816789818663</v>
+        <v>0.05793293131121707</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.698337824417076</v>
+        <v>2.784216483942718</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.628265901302259</v>
+        <v>-4.449641799690433</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7361496603219895</v>
+        <v>0.8075993009667206</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1037690524253604</v>
+        <v>0.03936204678404331</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.525551013701425</v>
+        <v>2.611429673227067</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.73687997974559</v>
+        <v>-4.558255878133764</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8128536896638627</v>
+        <v>0.8843033303085936</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1037690524253604</v>
+        <v>0.03936204678404331</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.645700674420631</v>
+        <v>2.731579333946273</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.823478562726693</v>
+        <v>-4.644854461114867</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.7927272825737446</v>
+        <v>0.8641769232184755</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1037690524253604</v>
+        <v>0.03936204678404331</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.660213700522954</v>
+        <v>2.746092360048596</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.785094900168542</v>
+        <v>-4.606470798556716</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8055001889393736</v>
+        <v>0.8769498295841047</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.06538538986720921</v>
+        <v>0.07774570934219449</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.680663339400213</v>
+        <v>2.766541998925855</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.607978570133376</v>
+        <v>-4.42935446852155</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.873075749798742</v>
+        <v>0.9445253904434729</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.06538538986720921</v>
+        <v>0.07774570934219449</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.677392368245515</v>
+        <v>2.763271027771157</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.653070814966922</v>
+        <v>-4.474446713355095</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8557222436272367</v>
+        <v>0.9271718842719678</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.127281433036599</v>
+        <v>0.0158496661728047</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.640938134105794</v>
+        <v>2.726816793631436</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.473695393728154</v>
+        <v>-4.295071292116328</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9212593874291581</v>
+        <v>0.9927090280738893</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.02949532513411968</v>
+        <v>0.1726264243435234</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.728791164314639</v>
+        <v>2.814669823840282</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.51870960724876</v>
+        <v>-4.340085505636933</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.8840611573525057</v>
+        <v>0.9555107979972366</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0008535701804849305</v>
+        <v>0.1422775290289188</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.691389282457467</v>
+        <v>2.777267941983109</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509534</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.785714117521195</v>
+        <v>-4.607090015909368</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.7829509155824774</v>
+        <v>0.8544005562272083</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1952166082234335</v>
+        <v>-0.05208550901402981</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.580463021970643</v>
+        <v>2.666341681496285</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.886911898958368</v>
+        <v>-4.708287797346541</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7416757249041097</v>
+        <v>0.8131253655488409</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2636254217687527</v>
+        <v>-0.120494322559349</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538621655739953</v>
+        <v>2.624500315265595</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.854436312787596</v>
+        <v>-4.675812211175769</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7522659209267353</v>
+        <v>0.8237155615714664</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2636254217687527</v>
+        <v>-0.120494322559349</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.53622161729427</v>
+        <v>2.622100276819912</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.835398185080298</v>
+        <v>-4.656774083468472</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7564058912178993</v>
+        <v>0.8278555318626302</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3218090330999472</v>
+        <v>-0.1786779338905435</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497836169703798</v>
+        <v>2.58371482922944</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.866524816230917</v>
+        <v>-4.68790071461909</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9215371076963323</v>
+        <v>0.9929867483410635</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3218090330999472</v>
+        <v>-0.1786779338905435</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.675418038642479</v>
+        <v>2.761296698168121</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.880391577564835</v>
+        <v>-4.701767475953008</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9168237321488988</v>
+        <v>0.9882733727936297</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3596669498337702</v>
+        <v>-0.2165358506243665</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.653536617588319</v>
+        <v>2.739415277113961</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.900648876093793</v>
+        <v>-4.722024774481966</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9147293431342416</v>
+        <v>0.9861789837789725</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3596669498337702</v>
+        <v>-0.2165358506243665</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.659545147985245</v>
+        <v>2.745423807510887</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.937163225079544</v>
+        <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.75290590585879</v>
+        <v>-4.70864307548544</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.035644438422281</v>
+        <v>1.070684311169605</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.191859592598887</v>
+        <v>-0.2276448366723703</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.822047469520212</v>
+        <v>2.817911063674106</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.939956846611025</v>
+        <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.854920588390011</v>
+        <v>-4.810657758016661</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9976321869412732</v>
+        <v>1.032672059688597</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.191859592598887</v>
+        <v>-0.2276448366723703</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.824841091051693</v>
+        <v>2.820704685205587</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.805608985394728</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.940619195002684</v>
+        <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.848767882337227</v>
+        <v>-4.804505051963877</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.000755617754045</v>
+        <v>1.03579549050137</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1857068865461027</v>
+        <v>-0.2214921306195861</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.829195063075022</v>
+        <v>2.825058657228916</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823979489061</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.939699671742794</v>
+        <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.865577180487729</v>
+        <v>-4.821314350114378</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9931123752339548</v>
+        <v>1.028152247981279</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2025161846966044</v>
+        <v>-0.2383014287700877</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.818189960924832</v>
+        <v>2.814053555078726</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>3.006035225539615</v>
+        <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.803279181711607</v>
+        <v>-4.759016351338256</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.084367128541225</v>
+        <v>1.119407001288549</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2025161846966044</v>
+        <v>-0.2383014287700877</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.884525514721652</v>
+        <v>2.880389108875546</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.714616097929013</v>
+        <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.601488984046449</v>
+        <v>-4.557226153673098</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8736640799966857</v>
+        <v>0.9087039527440099</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.004497992527449979</v>
+        <v>-0.0402832366009333</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.711917302412543</v>
+        <v>2.707780896566437</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852422</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.784906330251188</v>
+        <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.541598302403855</v>
+        <v>-4.497335472030505</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9679105849758982</v>
+        <v>1.002950457723223</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.0553926891151435</v>
+        <v>0.01960744504166018</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.818141943720275</v>
+        <v>2.814005537874168</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.799534066367232</v>
+        <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.63933884702883</v>
+        <v>-4.595076016655479</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9434421032419522</v>
+        <v>0.9784819759892764</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.03950341098216331</v>
+        <v>0.003718166908679987</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.82323611295653</v>
+        <v>2.819099707110424</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489383</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.798070047191903</v>
+        <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.815676607151759</v>
+        <v>-4.771413776778409</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.8714429800174521</v>
+        <v>0.9064828527647764</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1368343491407661</v>
+        <v>-0.1726195932142494</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.715969437707444</v>
+        <v>2.711833031861338</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397793</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.796561665231832</v>
+        <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.744130284374882</v>
+        <v>-4.699867454001532</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.8985531271681315</v>
+        <v>0.9335929999154557</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1368343491407661</v>
+        <v>-0.1726195932142494</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.714461055747373</v>
+        <v>2.710324649901267</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024961</v>
+        <v>3.836023391024959</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.796424532667268</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.699757152736313</v>
+        <v>-4.655494322362963</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9161652472589952</v>
+        <v>0.9512051200063194</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.09246121750219749</v>
+        <v>-0.1282464615756808</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.74094780216595</v>
+        <v>2.736811396319843</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863224</v>
+        <v>3.821591150863221</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.796424532667268</v>
+        <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.691803182441541</v>
+        <v>-4.647540352068191</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9193468353769041</v>
+        <v>0.9543867081242283</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.09246121750219749</v>
+        <v>-0.1282464615756808</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.74094780216595</v>
+        <v>2.736811396319843</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833040181947583</v>
+        <v>3.83304018194758</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.802806289695073</v>
+        <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.644147451880485</v>
+        <v>-4.599884621507135</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9447908846291311</v>
+        <v>0.9798307573764553</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.04480548694114184</v>
+        <v>-0.08059073101462516</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.775922997530388</v>
+        <v>2.771786591684282</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326875</v>
+        <v>3.822707244326873</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.807698663069798</v>
+        <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.516463142086189</v>
+        <v>-4.472200311712839</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.000756981921574</v>
+        <v>1.035796854668899</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.08287882285315462</v>
+        <v>0.0470935787796713</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.85742595678169</v>
+        <v>2.853289550935584</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314551</v>
+        <v>3.828837911314548</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.79445333554567</v>
+        <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.577129732488578</v>
+        <v>-4.532866902115227</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9632450182364907</v>
+        <v>0.9982848909838153</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.001180506134620951</v>
+        <v>-0.03460473793886237</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.795161639226443</v>
+        <v>2.791025233380336</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690027</v>
+        <v>3.816866067690024</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.798551038156298</v>
+        <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.53229133088018</v>
+        <v>-4.488028500506829</v>
       </c>
       <c r="E1981" t="n">
-        <v>0.9852780814904787</v>
+        <v>1.020317954237803</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.005723939079490425</v>
+        <v>-0.0300613049939929</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.801985401603993</v>
+        <v>2.797848995757886</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674311</v>
+        <v>3.817961388674307</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.802711977787376</v>
+        <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.633049966637178</v>
+        <v>-4.588787136263827</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9491355668187575</v>
+        <v>0.9841754395660822</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.083101629647515</v>
+        <v>-0.1188868737209983</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.752850999998868</v>
+        <v>2.748714594152761</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.82671377916322</v>
+        <v>3.826713779163216</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.808591580315213</v>
+        <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.588847129551278</v>
+        <v>-4.544584299177926</v>
       </c>
       <c r="E1983" t="n">
-        <v>0.9726963041809549</v>
+        <v>1.00773617692828</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.03889879256161455</v>
+        <v>-0.07468403663509787</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.785252304778245</v>
+        <v>2.781115898932139</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022905</v>
+        <v>3.838228663022901</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.807001580784461</v>
+        <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.62582615721472</v>
+        <v>-4.581563326841369</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9563146935848252</v>
+        <v>0.9913545663321499</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.001924890770284016</v>
+        <v>-0.03771013484376734</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.805846646322291</v>
+        <v>2.801710240476185</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042139</v>
+        <v>3.863924114042136</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.858249345967501</v>
+        <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.645884236079561</v>
+        <v>-4.60162140570621</v>
       </c>
       <c r="E1985" t="n">
-        <v>0.9995392272219288</v>
+        <v>1.034579099969253</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.001924890770284016</v>
+        <v>-0.03771013484376734</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.857094411505331</v>
+        <v>2.852958005659224</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078281</v>
+        <v>3.865367715078278</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.856690050561754</v>
+        <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.580990714723294</v>
+        <v>-4.561690732528319</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.023937340358689</v>
+        <v>1.048992073834663</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.06296863058598312</v>
+        <v>0.002220538334123001</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.894471228913344</v>
+        <v>2.875357114160212</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232397</v>
+        <v>3.864518876232395</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.851638278800024</v>
+        <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.540520367160589</v>
+        <v>-4.521220384965615</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.035073707622041</v>
+        <v>1.060128441098015</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.1034389781486881</v>
+        <v>0.04269088589682796</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.913701665689237</v>
+        <v>2.894587550936105</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162112</v>
+        <v>3.842576394162111</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.868825682892729</v>
+        <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.475296186033384</v>
+        <v>-4.455996203838409</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.078350784165628</v>
+        <v>1.103405517641602</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1686631592758937</v>
+        <v>0.1079150670240336</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.970023578458265</v>
+        <v>2.950909463705133</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639818</v>
+        <v>3.840090220639816</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.864786655192009</v>
+        <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.52579047639044</v>
+        <v>-4.506490494195465</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.054114040322086</v>
+        <v>1.07916877379806</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1236424221498195</v>
+        <v>0.06289432989795934</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.938972108481901</v>
+        <v>2.919857993728769</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.84519884274992</v>
+        <v>3.845198842749919</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.866043447523249</v>
+        <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.545902132425148</v>
+        <v>-4.526602150230174</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.047326170239443</v>
+        <v>1.072380903715417</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.1346697671472387</v>
+        <v>0.07392167489537854</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.946845307811593</v>
+        <v>2.927731193058461</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393545</v>
+        <v>3.828690479393544</v>
       </c>
       <c r="C1991" t="n">
-        <v>3.02660121854446</v>
+        <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.643582711697793</v>
+        <v>-4.62428272950282</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.168811709551595</v>
+        <v>1.193866443027569</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.02396657180704986</v>
+        <v>-0.03678152044481026</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.04098116162869</v>
+        <v>3.021867046875558</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714883</v>
+        <v>3.813251854714882</v>
       </c>
       <c r="C1992" t="n">
-        <v>3.146714127762277</v>
+        <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.619791143091651</v>
+        <v>-4.600491160896677</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.29844124621187</v>
+        <v>1.323495979687843</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.04775814041319215</v>
+        <v>-0.01298995183866797</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.175369012010193</v>
+        <v>3.156254897257061</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814259761756012</v>
+        <v>3.81425976175601</v>
       </c>
       <c r="C1993" t="n">
-        <v>3.138422103776136</v>
+        <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.656545561653373</v>
+        <v>-4.6372455794584</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.275447454801039</v>
+        <v>1.300502188277013</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.04775814041319215</v>
+        <v>-0.01298995183866797</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.167076988024052</v>
+        <v>3.14796287327092</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654186</v>
+        <v>3.803426852654185</v>
       </c>
       <c r="C1994" t="n">
-        <v>3.136615299359916</v>
+        <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.652211258596325</v>
+        <v>-4.632911276401352</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.275374371607638</v>
+        <v>1.300429105083612</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1994082437323961</v>
+        <v>0.138660151480536</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.256260245599354</v>
+        <v>3.237146130846221</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717117</v>
+        <v>3.796293177717115</v>
       </c>
       <c r="C1995" t="n">
-        <v>3.154169705086707</v>
+        <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.643318797203042</v>
+        <v>-4.624018815008069</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.296485761891743</v>
+        <v>1.321540495367716</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1994082437323961</v>
+        <v>0.138660151480536</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.273814651326145</v>
+        <v>3.254700536573013</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702625</v>
+        <v>3.794453975702623</v>
       </c>
       <c r="C1996" t="n">
-        <v>3.146024752491291</v>
+        <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.811794914172919</v>
+        <v>-4.792494931977946</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.220950362508376</v>
+        <v>1.246005095984349</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1714604080158153</v>
+        <v>0.1107123157639552</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.248900997300781</v>
+        <v>3.229786882547649</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539971</v>
+        <v>3.795603100539969</v>
       </c>
       <c r="C1997" t="n">
-        <v>3.216437413948135</v>
+        <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.661308232576869</v>
+        <v>-4.642008250381895</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.35155769660364</v>
+        <v>1.376612430079613</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1328120378583857</v>
+        <v>0.07206394560652563</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.296124636663166</v>
+        <v>3.277010521910035</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78415660239736</v>
+        <v>3.826162582283197</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.229547303820981</v>
+        <v>3.333802277927013</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.661308232576869</v>
+        <v>-4.642008250381895</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.35155769660364</v>
+        <v>1.376612430079613</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1328120378583857</v>
+        <v>0.07206394560652563</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.222611100807348</v>
+        <v>3.326866074913381</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,12 +610,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>47.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>21.8%</t>
+          <t>5.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.1%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104.9%</t>
+          <t>106.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.73</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.5%</t>
+          <t>124.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>85.8%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,27 +977,27 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.3%</t>
+          <t>-683.2%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.8%</t>
+          <t>-51.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-73.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>453.1%</t>
+          <t>452.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-625.8%</t>
+          <t>-630.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-273.7%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,22 +1155,22 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.2%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-40.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>50.2%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-238.6%</t>
+          <t>-246.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.4%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,27 +1293,27 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-277.4%</t>
+          <t>-291.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.5%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>119.1%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-173.3%</t>
+          <t>-196.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-216.8%</t>
+          <t>-212.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>56.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-166.8%</t>
+          <t>-175.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-27.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-16.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-113.3%</t>
+          <t>-121.6%</t>
         </is>
       </c>
     </row>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.802885748115715</v>
+        <v>-4.981509849727543</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202560810470751</v>
+        <v>1.131111169826019</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5403280785412382</v>
+        <v>-0.683459177750642</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.799874686906041</v>
+        <v>2.713996027380399</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.037579742248267</v>
+        <v>-5.216203843860096</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.09696798781982</v>
+        <v>1.025518347175089</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.533991811311983</v>
+        <v>-0.6771229105213868</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.791961222245685</v>
+        <v>2.706082562720043</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.37324238947872</v>
+        <v>-5.551866491090548</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9612835205836046</v>
+        <v>0.8898338799388732</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.533991811311983</v>
+        <v>-0.6771229105213868</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.79054181390165</v>
+        <v>2.704663154376008</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.736868634379033</v>
+        <v>-5.915492735990862</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8223205828577207</v>
+        <v>0.7508709422129893</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6322134481791089</v>
+        <v>-0.7753445473885127</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.738096392015616</v>
+        <v>2.652217732489974</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.10199601701778</v>
+        <v>-6.280620118629608</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6755241448080533</v>
+        <v>0.604074504163322</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.9285242324781213</v>
+        <v>-1.071655331687525</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.55956443644204</v>
+        <v>2.473685776916398</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.510584794198458</v>
+        <v>-6.689208895810287</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510850177950541</v>
+        <v>0.4394005373058096</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.3371130096588</v>
+        <v>-1.480244108868204</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.313172714148392</v>
+        <v>2.22729405462275</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.78716089451429</v>
+        <v>-6.96578499612612</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3954051702956689</v>
+        <v>0.3239555296509371</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.3371130096588</v>
+        <v>-1.480244108868204</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.308358146619853</v>
+        <v>2.22247948709421</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.203552768801288</v>
+        <v>-7.382176870413117</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2268424711897472</v>
+        <v>0.1553928305450154</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.3371130096588</v>
+        <v>-1.480244108868204</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.30635219722873</v>
+        <v>2.220473537703088</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.474318857893933</v>
+        <v>-7.652942959505762</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.128794726221368</v>
+        <v>0.0573450855766362</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.3371130096588</v>
+        <v>-1.480244108868204</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.316610887897409</v>
+        <v>2.230732228371767</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.820193679878741</v>
+        <v>-7.998817781490571</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.01345563742686018</v>
+        <v>-0.08490527807159198</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.3371130096588</v>
+        <v>-1.480244108868204</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.312710453043104</v>
+        <v>2.226831793517462</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.983773558063126</v>
+        <v>-8.162397659674955</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.08048266864561304</v>
+        <v>-0.1519323092903444</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.3371130096588</v>
+        <v>-1.480244108868204</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.311115373098105</v>
+        <v>2.225236713572463</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.280434899873324</v>
+        <v>-8.459059001485153</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.1953682294404842</v>
+        <v>-0.2668178700852155</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.405856145392678</v>
+        <v>-1.548987244602082</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.273648467586986</v>
+        <v>2.187769808061344</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.467154608182627</v>
+        <v>-8.645778709794456</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.274082417298608</v>
+        <v>-0.3455320579433399</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.405856145392678</v>
+        <v>-1.548987244602082</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.269622163052583</v>
+        <v>2.183743503526941</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.850155996925258</v>
+        <v>-9.028780098537087</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4273850741172449</v>
+        <v>-0.4988347147619763</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.405856145392678</v>
+        <v>-1.548987244602082</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.269520061730999</v>
+        <v>2.183641402205357</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.032025787910293</v>
+        <v>-9.210649889522122</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4975614745398285</v>
+        <v>-0.5690111151845603</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.587725936377713</v>
+        <v>-1.730857035587117</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.162969703111408</v>
+        <v>2.077091043585766</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.391556110414294</v>
+        <v>-9.570180212026123</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6360233002433788</v>
+        <v>-0.7074729408881106</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.587725936377713</v>
+        <v>-1.730857035587117</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.168320006409458</v>
+        <v>2.082441346883816</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.441905173868516</v>
+        <v>-9.620529275480346</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6482469056678903</v>
+        <v>-0.7196965463126221</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.638074999831935</v>
+        <v>-1.781206099041339</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.146026588294103</v>
+        <v>2.06014792876846</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.539524451289912</v>
+        <v>-9.718148552901742</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6842528660146798</v>
+        <v>-0.7557025066594116</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.735694277253332</v>
+        <v>-1.878825376462736</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.090496772463033</v>
+        <v>2.004618112937391</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.687050539295555</v>
+        <v>-9.865674640907384</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7403697448953648</v>
+        <v>-0.8118193855400966</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.883220365258976</v>
+        <v>-2.02635146446838</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.004874675981219</v>
+        <v>1.918996016455577</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.891308714625419</v>
+        <v>-10.06993281623725</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.8165598179086677</v>
+        <v>-0.8880094585534</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.010859309872965</v>
+        <v>-2.153990409082369</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.933804506331469</v>
+        <v>1.847925846805826</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.965641690885583</v>
+        <v>-10.14426579249741</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8418104539282978</v>
+        <v>-0.9132600945730291</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.155558833807637</v>
+        <v>-2.298689933017041</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.851467346455101</v>
+        <v>1.765588686929459</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.892171859218134</v>
+        <v>-10.07079596082996</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7970508197678967</v>
+        <v>-0.868500460412629</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.082089002140189</v>
+        <v>-2.225220101349593</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.910920946948991</v>
+        <v>1.825042287423349</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.06729627660468</v>
+        <v>-10.24592037821651</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8525453659749971</v>
+        <v>-0.9239950066197293</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.257213419526733</v>
+        <v>-2.400344518736137</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.820401517264582</v>
+        <v>1.734522857738939</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.30174837061917</v>
+        <v>-10.480372472231</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9535453684823891</v>
+        <v>-1.024995009127121</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.257213419526733</v>
+        <v>-2.400344518736137</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.813182352362986</v>
+        <v>1.727303692837343</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.40612310164561</v>
+        <v>-10.58474720325744</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.001967451666944</v>
+        <v>-1.073417092311676</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.361588150553179</v>
+        <v>-2.504719249762582</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.743885322973142</v>
+        <v>1.6580066634475</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.45890925724594</v>
+        <v>-10.63753335885777</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.021966124068518</v>
+        <v>-1.09341576471325</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.457263637135576</v>
+        <v>-2.600394736344979</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.68759582086226</v>
+        <v>1.601717161336618</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.58494605061423</v>
+        <v>-10.76357015222606</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.069687112786719</v>
+        <v>-1.141136753431451</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.432012014325833</v>
+        <v>-2.575143113535237</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.70544052317722</v>
+        <v>1.619561863651578</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.53293053664542</v>
+        <v>-10.71155463825725</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.044890571512793</v>
+        <v>-1.116340212157525</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.432012014325833</v>
+        <v>-2.575143113535237</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.709430858863621</v>
+        <v>1.623552199337979</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.67460237836954</v>
+        <v>-10.85322647998137</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.103034535101183</v>
+        <v>-1.174484175745915</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.432012014325833</v>
+        <v>-2.575143113535237</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.707955631964879</v>
+        <v>1.622076972439237</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.6250115339447</v>
+        <v>-10.80363563555653</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.068144787166377</v>
+        <v>-1.139594427811109</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.382421169900999</v>
+        <v>-2.525552269110403</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.752763548784652</v>
+        <v>1.66688488925901</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.61220414093993</v>
+        <v>-10.79082824255176</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.07607296361115</v>
+        <v>-1.147522604255883</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.431276944909901</v>
+        <v>-2.574408044119304</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.710398950132628</v>
+        <v>1.624520290606986</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.38635898822052</v>
+        <v>-10.56498308983235</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.9761558294871775</v>
+        <v>-1.047605470131909</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.389350269322737</v>
+        <v>-2.532481368532141</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.745134028521135</v>
+        <v>1.659255368995493</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.26178033188293</v>
+        <v>-10.44040443349475</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9251852223960824</v>
+        <v>-0.9966348630408128</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.389350269322737</v>
+        <v>-2.532481368532141</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.746273173077194</v>
+        <v>1.660394513551552</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.31467561992721</v>
+        <v>-10.49329972153904</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.943709563451689</v>
+        <v>-1.01515920409642</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.384394923234291</v>
+        <v>-2.527526022443694</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.751880154892369</v>
+        <v>1.666001495366727</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611568</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.24254244463933</v>
+        <v>-10.42116654625116</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9091225890979002</v>
+        <v>-0.9805722297426316</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.384394923234291</v>
+        <v>-2.527526022443694</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.757613859131006</v>
+        <v>1.671735199605364</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.17117605202968</v>
+        <v>-10.34325704877462</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8903132944479069</v>
+        <v>-0.9591456931458815</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.313028530624643</v>
+        <v>-2.449616524967157</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.79069643230293</v>
+        <v>1.708743635697421</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.907339184825615</v>
+        <v>-10.07942018157055</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7946620288791864</v>
+        <v>-0.863494427577161</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.313028530624643</v>
+        <v>-2.449616524967157</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.780812950990022</v>
+        <v>1.698860154384513</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.640097383957217</v>
+        <v>-9.812178380702154</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6895998690312006</v>
+        <v>-0.7584322677291753</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.313028530624643</v>
+        <v>-2.449616524967157</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.778978390490648</v>
+        <v>1.69702559388514</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.542190345280726</v>
+        <v>-9.714271342025663</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6507373685340654</v>
+        <v>-0.71956976723204</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.245042780764086</v>
+        <v>-2.381630775106601</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.819469525433521</v>
+        <v>1.737516728828012</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.518236804304768</v>
+        <v>-9.690317801049705</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6404874459981884</v>
+        <v>-0.709319844696163</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.221089239788129</v>
+        <v>-2.357677234130643</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.834510156164589</v>
+        <v>1.752557359559081</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.254176865981972</v>
+        <v>-9.426257862726908</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5481237868308222</v>
+        <v>-0.6169561855287968</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.957029301465332</v>
+        <v>-2.093617295807847</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.979685802996515</v>
+        <v>1.897733006391006</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.547097242477134</v>
+        <v>-8.719178239222071</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2680789710891878</v>
+        <v>-0.3369113697871624</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.957029301465332</v>
+        <v>-2.093617295807847</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.976898769336214</v>
+        <v>1.894945972730705</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.506912944110944</v>
+        <v>-8.67899394085588</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2516616278548702</v>
+        <v>-0.3204940265528449</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.916845003099142</v>
+        <v>-2.053432997441656</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.00135297224377</v>
+        <v>1.919400175638261</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.343513073171582</v>
+        <v>-8.515594069916517</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1869348582583688</v>
+        <v>-0.2557672569563429</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.753445132159779</v>
+        <v>-1.890033126502294</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.098759716028144</v>
+        <v>2.016806919422636</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.110031850941983</v>
+        <v>-8.282112847686918</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08561794052867677</v>
+        <v>-0.1544503392266505</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.519963909930181</v>
+        <v>-1.656551904272695</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.246772878203756</v>
+        <v>2.164820081598247</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.960365459934468</v>
+        <v>-8.132446456679403</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02864359443862963</v>
+        <v>-0.09747599313660427</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.427060418687645</v>
+        <v>-1.563648413030159</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.299622762636318</v>
+        <v>2.217669966030809</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.828089986303581</v>
+        <v>-8.000170983048516</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.01963408176075188</v>
+        <v>-0.04919831693722232</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.294784945056758</v>
+        <v>-1.431372939399273</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.374355533561877</v>
+        <v>2.292402736956368</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.637490311630429</v>
+        <v>-7.809571308375364</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.09868901231764937</v>
+        <v>0.02985661361967518</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.104185270383605</v>
+        <v>-1.24077326472612</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.491530399053405</v>
+        <v>2.409577602447897</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.388490512946848</v>
+        <v>-7.560571509691782</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2111952730147406</v>
+        <v>0.1423628743167664</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.104185270383605</v>
+        <v>-1.24077326472612</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.504436740277064</v>
+        <v>2.422483943671556</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.494080502719952</v>
+        <v>-7.666161499464887</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.04098334750628041</v>
+        <v>-0.02784905119169423</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.20977526015671</v>
+        <v>-1.346363254499224</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.313106816813983</v>
+        <v>2.231154020208474</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.512815404838549</v>
+        <v>-7.684896401583484</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08203372853592761</v>
+        <v>0.01320132983795341</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.215371269816841</v>
+        <v>-1.351959264159355</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.35829355289499</v>
+        <v>2.276340756289482</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.36487536343095</v>
+        <v>-7.536956360175885</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02133082241079975</v>
+        <v>-0.04750157628717444</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.195050353908283</v>
+        <v>-1.331638348250798</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.250607179751958</v>
+        <v>2.168654383146449</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.311905841176961</v>
+        <v>-7.483986837921896</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.03380464505891734</v>
+        <v>-0.0350277536390573</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.142080831654294</v>
+        <v>-1.278668825996809</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.273674906850873</v>
+        <v>2.191722110245364</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.268357434406271</v>
+        <v>-7.440438431151206</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.04426339567210036</v>
+        <v>-0.02456900302587428</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.142080831654294</v>
+        <v>-1.278668825996809</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.26671429475578</v>
+        <v>2.184761498150271</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.026209040952413</v>
+        <v>-7.198290037697348</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1555851074347867</v>
+        <v>0.08675270873681207</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.142080831654294</v>
+        <v>-1.278668825996809</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.281176649136923</v>
+        <v>2.199223852531414</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.917949903829891</v>
+        <v>-7.090030900574826</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1934208827429904</v>
+        <v>0.1245884840450158</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.142080831654294</v>
+        <v>-1.278668825996809</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.275708769596118</v>
+        <v>2.193755972990609</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.79465876901276</v>
+        <v>-6.966739765757695</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2402354306804195</v>
+        <v>0.1714030319824453</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.018789696837164</v>
+        <v>-1.155377691179678</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.347181544496973</v>
+        <v>2.265228747891464</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.773509570109317</v>
+        <v>-6.945590566854252</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2563960884791219</v>
+        <v>0.1875636897811477</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.9976404979337206</v>
+        <v>-1.134228492276235</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.367572042076364</v>
+        <v>2.285619245470855</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.529744128125873</v>
+        <v>-6.701825124870807</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3496829736195504</v>
+        <v>0.2808505749215762</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.9976404979337206</v>
+        <v>-1.134228492276235</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.363352750423415</v>
+        <v>2.281399953817906</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.427981307848578</v>
+        <v>-6.600062304593513</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3925124156504842</v>
+        <v>0.32368001695251</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.9844214295412919</v>
+        <v>-1.121009423883806</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.373408505378888</v>
+        <v>2.291455708773379</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.178130913899503</v>
+        <v>-6.350211910644438</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4851946482138163</v>
+        <v>0.4163622495158421</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.9844214295412919</v>
+        <v>-1.121009423883806</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.36615058036259</v>
+        <v>2.284197783757081</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.002238821432071</v>
+        <v>-6.174319818177005</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.559150608721438</v>
+        <v>0.4903182100234638</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.9844214295412919</v>
+        <v>-1.121009423883806</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.369749703883239</v>
+        <v>2.28779690727773</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.830792358409608</v>
+        <v>-6.002873355154541</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6410566999849769</v>
+        <v>0.5722243012870032</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.8129749665188287</v>
+        <v>-0.9495629608613433</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.48594508775127</v>
+        <v>2.403992291145761</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.756502792671268</v>
+        <v>-5.928583789416202</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6697930038966096</v>
+        <v>0.6009606051986358</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7386854007804895</v>
+        <v>-0.8752733951230041</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.529539304810571</v>
+        <v>2.447586508205062</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.692867050437334</v>
+        <v>-5.864948047182268</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6999421018445009</v>
+        <v>0.6311097031465267</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.675049658546555</v>
+        <v>-0.8116376528890695</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.572415551205249</v>
+        <v>2.49046275459974</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.649104869131492</v>
+        <v>-5.821185865876426</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6986412331506329</v>
+        <v>0.6298088344526591</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.675049658546555</v>
+        <v>-0.8116376528890695</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.553609809989045</v>
+        <v>2.471657013383536</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.408674372326632</v>
+        <v>-5.580755369071566</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7965565084974546</v>
+        <v>0.7277241097994804</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4346191617416947</v>
+        <v>-0.5712071560842092</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.699611184696838</v>
+        <v>2.617658388091329</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.336431804155437</v>
+        <v>-5.508512800900371</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8293828496007527</v>
+        <v>0.7605504509027785</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4346191617416947</v>
+        <v>-0.5712071560842092</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.703540498531658</v>
+        <v>2.62158770192615</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.28343348187405</v>
+        <v>-5.455514478618984</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8512607624306479</v>
+        <v>0.7824283637326737</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3792829027397558</v>
+        <v>-0.5158708970822704</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.737420837850161</v>
+        <v>2.655468041244653</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.174628596394323</v>
+        <v>-5.346709593139257</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8917807878425319</v>
+        <v>0.8229483891445581</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3792829027397558</v>
+        <v>-0.5158708970822704</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.734418909070155</v>
+        <v>2.652466112464646</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.954607798357312</v>
+        <v>-5.126688795102246</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9813681440679503</v>
+        <v>0.9125357453699765</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2380630576717756</v>
+        <v>-0.3746510520142902</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.820729853121557</v>
+        <v>2.738777056516049</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.821740109294034</v>
+        <v>-4.993821106038968</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.050409402495085</v>
+        <v>0.9815770037971108</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2380630576717756</v>
+        <v>-0.3746510520142902</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.836624035923381</v>
+        <v>2.754671239317872</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.701567025929536</v>
+        <v>-4.87364802267447</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.099624480281186</v>
+        <v>1.030792081583212</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1178899743072767</v>
+        <v>-0.2544779686497912</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.909873730382382</v>
+        <v>2.827920933776873</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.556894880829798</v>
+        <v>-4.728975877574732</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.167581440882521</v>
+        <v>1.098749042184547</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.02678217079246076</v>
+        <v>-0.1098058235500538</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.006765120003664</v>
+        <v>2.924812323398156</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.616769708187491</v>
+        <v>-4.788850704932424</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.12966900134087</v>
+        <v>1.060836602642896</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.03309265656523136</v>
+        <v>-0.1696806509077459</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.956877714990475</v>
+        <v>2.874924918384966</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.529970210408482</v>
+        <v>-4.702051207153416</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.186789293775039</v>
+        <v>1.117956895077065</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.03309265656523136</v>
+        <v>-0.1696806509077459</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.979278208313041</v>
+        <v>2.897325411707532</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.532439916870288</v>
+        <v>-4.704520913615222</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.185873812563729</v>
+        <v>1.117041413865755</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.03556236302703752</v>
+        <v>-0.1721503573695521</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.977868785809369</v>
+        <v>2.895915989203861</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.600810103194299</v>
+        <v>-4.772891099939232</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.169532660508827</v>
+        <v>1.100700261810853</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.02628666399082258</v>
+        <v>-0.1628746583333371</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.9944411277058</v>
+        <v>2.912488331100291</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.709348284110432</v>
+        <v>-4.881429280855366</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.116554096774265</v>
+        <v>1.047721698076291</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.02628666399082258</v>
+        <v>-0.1628746583333371</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.984877836337692</v>
+        <v>2.902925039732183</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.740341443439138</v>
+        <v>-4.856798408577677</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9288663980831693</v>
+        <v>0.8822836120277533</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.02628666399082258</v>
+        <v>-0.1628746583333371</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.809587401378078</v>
+        <v>2.727634604772569</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.564867183646669</v>
+        <v>-4.681324148785207</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.003623333991944</v>
+        <v>0.9570405479365289</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.02628666399082258</v>
+        <v>-0.1628746583333371</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.814154633369866</v>
+        <v>2.732201836764357</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.675803436287918</v>
+        <v>-4.792260401426456</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.934990861696652</v>
+        <v>0.8884080756412365</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.02628666399082258</v>
+        <v>-0.1628746583333371</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.789896662131073</v>
+        <v>2.707943865525564</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.684085510432976</v>
+        <v>-4.800542475571515</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9348094172585342</v>
+        <v>0.8882266312031186</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.03456873813588096</v>
+        <v>-0.1711567324783955</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.788058802863944</v>
+        <v>2.706106006258435</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.624232891229253</v>
+        <v>-4.740689856367791</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9689228513721559</v>
+        <v>0.9223400653167402</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.03456873813588096</v>
+        <v>-0.1711567324783955</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.798231189296076</v>
+        <v>2.716278392690567</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.537989428202875</v>
+        <v>-4.654446393341414</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9983665071565673</v>
+        <v>0.9517837211011515</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.03456873813588096</v>
+        <v>-0.1711567324783955</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.793177459869936</v>
+        <v>2.711224663264427</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.583296247601855</v>
+        <v>-4.699753212740394</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9720195548415009</v>
+        <v>0.9254367687860852</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.07537890114511175</v>
+        <v>-0.2119668954876263</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.760467137508924</v>
+        <v>2.678514340903415</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.612329352304156</v>
+        <v>-4.728786317442695</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.960958185993682</v>
+        <v>0.9143753999382662</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.07537890114511175</v>
+        <v>-0.2119668954876263</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.761019010542025</v>
+        <v>2.679066213936516</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.519518870853297</v>
+        <v>-4.635975835991835</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9273550704653915</v>
+        <v>0.8807722844099759</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.0174315803057476</v>
+        <v>-0.119156414036767</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.745977991303906</v>
+        <v>2.664025194698397</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.563908340182724</v>
+        <v>-4.680365305321263</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9114727586582214</v>
+        <v>0.8648899726028056</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02695788902368007</v>
+        <v>-0.1635458833661946</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.72121778563085</v>
+        <v>2.639264989025342</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.451237121946474</v>
+        <v>-4.567694087085012</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9516169544644444</v>
+        <v>0.9050341684090286</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.08571332921257013</v>
+        <v>-0.05087466512994443</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.783896225084324</v>
+        <v>2.701943428478815</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.338860120763801</v>
+        <v>-4.455317085902339</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.002059050768181</v>
+        <v>0.955476264712765</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.08571332921257013</v>
+        <v>-0.05087466512994443</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.789387520914991</v>
+        <v>2.707434724309482</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.366640518665154</v>
+        <v>-4.483097483803692</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.002444093376179</v>
+        <v>0.9558613073207631</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.05793293131121707</v>
+        <v>-0.07865506303129749</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.784216483942718</v>
+        <v>2.702263687337209</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.449641799690433</v>
+        <v>-4.566098764828971</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8075993009667206</v>
+        <v>0.7610165149113048</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.03936204678404331</v>
+        <v>-0.09722594755847125</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.611429673227067</v>
+        <v>2.529476876621558</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.558255878133764</v>
+        <v>-4.674712843272302</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8843033303085936</v>
+        <v>0.8377205442531781</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.03936204678404331</v>
+        <v>-0.09722594755847125</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.731579333946273</v>
+        <v>2.649626537340764</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190767</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.644854461114867</v>
+        <v>-4.761311426253405</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8641769232184755</v>
+        <v>0.8175941371630597</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.03936204678404331</v>
+        <v>-0.09722594755847125</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.746092360048596</v>
+        <v>2.664139563443087</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.606470798556716</v>
+        <v>-4.722927763695254</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8769498295841047</v>
+        <v>0.830367043528689</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.07774570934219449</v>
+        <v>-0.05884228500032007</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.766541998925855</v>
+        <v>2.684589202320347</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.42935446852155</v>
+        <v>-4.545811433660088</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9445253904434729</v>
+        <v>0.8979426043880574</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.07774570934219449</v>
+        <v>-0.05884228500032007</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.763271027771157</v>
+        <v>2.681318231165648</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.474446713355095</v>
+        <v>-4.590903678493634</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9271718842719678</v>
+        <v>0.8805890982165521</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.0158496661728047</v>
+        <v>-0.1207383281697099</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.726816793631436</v>
+        <v>2.644863997025928</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.295071292116328</v>
+        <v>-4.411528257254866</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9927090280738893</v>
+        <v>0.9461262420184735</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.1726264243435234</v>
+        <v>0.03603843000100881</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.814669823840282</v>
+        <v>2.732717027234773</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.340085505636933</v>
+        <v>-4.456542470775472</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9555107979972366</v>
+        <v>0.908928011941821</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.1422775290289188</v>
+        <v>0.005689534686404207</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.777267941983109</v>
+        <v>2.6953151453776</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.607090015909368</v>
+        <v>-4.723546981047907</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8544005562272083</v>
+        <v>0.8078177701717928</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.05208550901402981</v>
+        <v>-0.1886735033565444</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.666341681496285</v>
+        <v>2.584388884890777</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.708287797346541</v>
+        <v>-4.824744762485079</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8131253655488409</v>
+        <v>0.7665425794934251</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.120494322559349</v>
+        <v>-0.2570823169018636</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.624500315265595</v>
+        <v>2.542547518660087</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.675812211175769</v>
+        <v>-4.792269176314307</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8237155615714664</v>
+        <v>0.7771327755160506</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.120494322559349</v>
+        <v>-0.2570823169018636</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.622100276819912</v>
+        <v>2.540147480214404</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.656774083468472</v>
+        <v>-4.77323104860701</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8278555318626302</v>
+        <v>0.7812727458072146</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.1786779338905435</v>
+        <v>-0.3152659282330581</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.58371482922944</v>
+        <v>2.501762032623931</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.68790071461909</v>
+        <v>-4.804357679757628</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9929867483410635</v>
+        <v>0.9464039622856477</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.1786779338905435</v>
+        <v>-0.3152659282330581</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.761296698168121</v>
+        <v>2.679343901562612</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.701767475953008</v>
+        <v>-4.818224441091546</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9882733727936297</v>
+        <v>0.9416905867382142</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2165358506243665</v>
+        <v>-0.353123844966881</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.739415277113961</v>
+        <v>2.657462480508452</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.722024774481966</v>
+        <v>-4.838481739620504</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9861789837789725</v>
+        <v>0.939596197723557</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2165358506243665</v>
+        <v>-0.353123844966881</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.745423807510887</v>
+        <v>2.663471010905378</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.70864307548544</v>
+        <v>-4.690738769385502</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.070684311169605</v>
+        <v>1.07784603360958</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.2276448366723703</v>
+        <v>-0.1853164877319979</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.817911063674106</v>
+        <v>2.84330807303833</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.810657758016661</v>
+        <v>-4.792753451916723</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.032672059688597</v>
+        <v>1.039833782128572</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.2276448366723703</v>
+        <v>-0.1853164877319979</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.820704685205587</v>
+        <v>2.846101694569811</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.804505051963877</v>
+        <v>-4.786600745863939</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.03579549050137</v>
+        <v>1.042957212941344</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2214921306195861</v>
+        <v>-0.1791637816792136</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.825058657228916</v>
+        <v>2.85045566659314</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.821314350114378</v>
+        <v>-4.80341004401444</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.028152247981279</v>
+        <v>1.035313970421254</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.2383014287700877</v>
+        <v>-0.1959730798297152</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.814053555078726</v>
+        <v>2.839450564442949</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.759016351338256</v>
+        <v>-4.741112045238318</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.119407001288549</v>
+        <v>1.126568723728524</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.2383014287700877</v>
+        <v>-0.1959730798297152</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.880389108875546</v>
+        <v>2.90578611823977</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.557226153673098</v>
+        <v>-4.53932184757316</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9087039527440099</v>
+        <v>0.9158656751839849</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.0402832366009333</v>
+        <v>0.002045112339439159</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.707780896566437</v>
+        <v>2.73317790593066</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.497335472030505</v>
+        <v>-4.479431165930567</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.002950457723223</v>
+        <v>1.010112180163197</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.01960744504166018</v>
+        <v>0.06193579398203264</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.814005537874168</v>
+        <v>2.839402547238392</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.595076016655479</v>
+        <v>-4.577171710555541</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9784819759892764</v>
+        <v>0.9856436984292514</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.003718166908679987</v>
+        <v>0.04604651584905245</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.819099707110424</v>
+        <v>2.844496716474647</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.771413776778409</v>
+        <v>-4.753509470678471</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9064828527647764</v>
+        <v>0.9136445752047513</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1726195932142494</v>
+        <v>-0.1302912442738769</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.711833031861338</v>
+        <v>2.737230041225561</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.699867454001532</v>
+        <v>-4.681963147901594</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9335929999154557</v>
+        <v>0.9407547223554307</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1726195932142494</v>
+        <v>-0.1302912442738769</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.710324649901267</v>
+        <v>2.73572165926549</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.655494322362963</v>
+        <v>-4.637590016263025</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9512051200063194</v>
+        <v>0.9583668424462943</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.1282464615756808</v>
+        <v>-0.08591811263530835</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.736811396319843</v>
+        <v>2.762208405684067</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.647540352068191</v>
+        <v>-4.629636045968253</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.9543867081242283</v>
+        <v>0.961548430564203</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.1282464615756808</v>
+        <v>-0.08591811263530835</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.736811396319843</v>
+        <v>2.762208405684067</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.599884621507135</v>
+        <v>-4.581980315407197</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.9798307573764553</v>
+        <v>0.98699247981643</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.08059073101462516</v>
+        <v>-0.0382623820742527</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.771786591684282</v>
+        <v>2.797183601048505</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.472200311712839</v>
+        <v>-4.454296005612901</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.035796854668899</v>
+        <v>1.042958577108873</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.0470935787796713</v>
+        <v>0.08942192772004376</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.853289550935584</v>
+        <v>2.878686560299808</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.532866902115227</v>
+        <v>-4.51496259601529</v>
       </c>
       <c r="E1980" t="n">
-        <v>0.9982848909838153</v>
+        <v>1.00544661342379</v>
       </c>
       <c r="F1980" t="n">
-        <v>-0.03460473793886237</v>
+        <v>0.007723611001510089</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.791025233380336</v>
+        <v>2.81642224274456</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.488028500506829</v>
+        <v>-4.470124194406892</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.020317954237803</v>
+        <v>1.027479676677778</v>
       </c>
       <c r="F1981" t="n">
-        <v>-0.0300613049939929</v>
+        <v>0.01226704394637956</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.797848995757886</v>
+        <v>2.82324600512211</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.588787136263827</v>
+        <v>-4.57088283016389</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9841754395660822</v>
+        <v>0.9913371620060567</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.1188868737209983</v>
+        <v>-0.07655852478062586</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.748714594152761</v>
+        <v>2.774111603516985</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.544584299177926</v>
+        <v>-4.526679993077989</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.00773617692828</v>
+        <v>1.014897899368254</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.07468403663509787</v>
+        <v>-0.03235568769472541</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.781115898932139</v>
+        <v>2.806512908296362</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.581563326841369</v>
+        <v>-4.563659020741432</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9913545663321499</v>
+        <v>0.9985162887721244</v>
       </c>
       <c r="F1984" t="n">
-        <v>-0.03771013484376734</v>
+        <v>0.004618214096605122</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.801710240476185</v>
+        <v>2.827107249840408</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.60162140570621</v>
+        <v>-4.583717099606273</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.034579099969253</v>
+        <v>1.041740822409228</v>
       </c>
       <c r="F1985" t="n">
-        <v>-0.03771013484376734</v>
+        <v>0.004618214096605122</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.852958005659224</v>
+        <v>2.878355015023448</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.561690732528319</v>
+        <v>-4.543786426428382</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.048992073834663</v>
+        <v>1.056153796274637</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.002220538334123001</v>
+        <v>0.04454888727449546</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.875357114160212</v>
+        <v>2.900754123524435</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.521220384965615</v>
+        <v>-4.503316078865677</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.060128441098015</v>
+        <v>1.067290163537989</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.04269088589682796</v>
+        <v>0.08501923483720042</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.894587550936105</v>
+        <v>2.919984560300328</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.455996203838409</v>
+        <v>-4.438091897738472</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.103405517641602</v>
+        <v>1.110567240081576</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.1079150670240336</v>
+        <v>0.150243415964406</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.950909463705133</v>
+        <v>2.976306473069356</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.506490494195465</v>
+        <v>-4.488586188095528</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.07916877379806</v>
+        <v>1.086330496238034</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.06289432989795934</v>
+        <v>0.1052226788383318</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.919857993728769</v>
+        <v>2.945255003092992</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.526602150230174</v>
+        <v>-4.508697844130237</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.072380903715417</v>
+        <v>1.079542626155391</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.07392167489537854</v>
+        <v>0.116250023835751</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.927731193058461</v>
+        <v>2.953128202422684</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.62428272950282</v>
+        <v>-4.606378423402883</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.193866443027569</v>
+        <v>1.201028165467543</v>
       </c>
       <c r="F1991" t="n">
-        <v>-0.03678152044481026</v>
+        <v>0.005546828495562206</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.021867046875558</v>
+        <v>3.047264056239781</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.600491160896677</v>
+        <v>-4.58258685479674</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.323495979687843</v>
+        <v>1.330657702127818</v>
       </c>
       <c r="F1992" t="n">
-        <v>-0.01298995183866797</v>
+        <v>0.02933839710170449</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.156254897257061</v>
+        <v>3.181651906621284</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.6372455794584</v>
+        <v>-4.619341273358462</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.300502188277013</v>
+        <v>1.307663910716988</v>
       </c>
       <c r="F1993" t="n">
-        <v>-0.01298995183866797</v>
+        <v>0.02933839710170449</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.14796287327092</v>
+        <v>3.173359882635143</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.632911276401352</v>
+        <v>-4.615006970301414</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.300429105083612</v>
+        <v>1.307590827523586</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.138660151480536</v>
+        <v>0.1809885004209084</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.237146130846221</v>
+        <v>3.262543140210445</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.624018815008069</v>
+        <v>-4.606114508908131</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.321540495367716</v>
+        <v>1.328702217807691</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.138660151480536</v>
+        <v>0.1809885004209084</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.254700536573013</v>
+        <v>3.280097545937236</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.792494931977946</v>
+        <v>-4.774590625878009</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.246005095984349</v>
+        <v>1.253166818424324</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1107123157639552</v>
+        <v>0.1530406647043276</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.229786882547649</v>
+        <v>3.255183891911872</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539969</v>
+        <v>3.795603100539968</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.642008250381895</v>
+        <v>-4.624103944281958</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.376612430079613</v>
+        <v>1.383774152519588</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.07206394560652563</v>
+        <v>0.1143922945468981</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.277010521910035</v>
+        <v>3.302407531274258</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.826162582283197</v>
+        <v>3.757881648454559</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.333802277927013</v>
+        <v>3.17564340766071</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.642008250381895</v>
+        <v>-4.685047028046715</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.376612430079613</v>
+        <v>1.301268172128276</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.07206394560652563</v>
+        <v>0.1143922945468981</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.326866074913381</v>
+        <v>3.244278784388849</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240617.xlsx
+++ b/tame_output/ON/bt/strategyON_20240617.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.5%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>10.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-77.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.8%</t>
+          <t>-73.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>452.4%</t>
+          <t>452.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-630.1%</t>
+          <t>-628.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.1%</t>
+          <t>-42.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-246.1%</t>
+          <t>-240.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-21.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-14.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-196.2%</t>
+          <t>-190.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-212.6%</t>
+          <t>-213.2%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>63.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.6%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-121.6%</t>
+          <t>-117.1%</t>
         </is>
       </c>
     </row>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191734</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108636</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.341378723097818</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094114</v>
+        <v>3.374439043094113</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199282</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.42463335496959</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937496</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141699</v>
+        <v>3.502790399141698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440632</v>
+        <v>3.499971739440631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764395</v>
+        <v>3.480692492764394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.676841549770578</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615282</v>
+        <v>3.685161381615281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.6848438238121</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646215</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955327</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.34325704877462</v>
+        <v>-10.34980015364151</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.9591456931458815</v>
+        <v>-0.9617629350926373</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.449616524967157</v>
+        <v>-2.456159629834046</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.708743635697421</v>
+        <v>1.704817772777287</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232411</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.07942018157055</v>
+        <v>-10.08596328643744</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.863494427577161</v>
+        <v>-0.8661116695239168</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.449616524967157</v>
+        <v>-2.456159629834046</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.698860154384513</v>
+        <v>1.69493429146438</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436227</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.812178380702154</v>
+        <v>-9.818721485569045</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7584322677291753</v>
+        <v>-0.761049509675932</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.449616524967157</v>
+        <v>-2.456159629834046</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.69702559388514</v>
+        <v>1.693099730965006</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311948</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.714271342025663</v>
+        <v>-9.720814446892554</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.71956976723204</v>
+        <v>-0.7221870091787963</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.381630775106601</v>
+        <v>-2.38817387997349</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.737516728828012</v>
+        <v>1.733590865907879</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097243</v>
+        <v>3.800829354097242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.690317801049705</v>
+        <v>-9.696860905916596</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.709319844696163</v>
+        <v>-0.7119370866429198</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.357677234130643</v>
+        <v>-2.364220338997532</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.752557359559081</v>
+        <v>1.748631496638947</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.78931111201777</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.426257862726908</v>
+        <v>-9.432800967593799</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.6169561855287968</v>
+        <v>-0.6195734274755531</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.093617295807847</v>
+        <v>-2.100160400674736</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.897733006391006</v>
+        <v>1.893807143470873</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839724</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.719178239222071</v>
+        <v>-8.725721344088962</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3369113697871624</v>
+        <v>-0.3395286117339191</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.093617295807847</v>
+        <v>-2.100160400674736</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.894945972730705</v>
+        <v>1.891020109810572</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388727</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.67899394085588</v>
+        <v>-8.685537045722771</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.3204940265528449</v>
+        <v>-0.3231112684996016</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.053432997441656</v>
+        <v>-2.059976102308545</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.919400175638261</v>
+        <v>1.915474312718128</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626473</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.515594069916517</v>
+        <v>-8.52213717478341</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2557672569563429</v>
+        <v>-0.2583844989030997</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.890033126502294</v>
+        <v>-1.896576231369183</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.016806919422636</v>
+        <v>2.012881056502502</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.282112847686918</v>
+        <v>-8.28865595255381</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1544503392266505</v>
+        <v>-0.1570675811734077</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.656551904272695</v>
+        <v>-1.663095009139584</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.164820081598247</v>
+        <v>2.160894218678114</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.132446456679403</v>
+        <v>-8.138989561546296</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09747599313660427</v>
+        <v>-0.100093235083361</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.563648413030159</v>
+        <v>-1.570191517897048</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.217669966030809</v>
+        <v>2.213744103110676</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390424</v>
       </c>
       <c r="C1905" t="n">
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.000170983048516</v>
+        <v>-8.006714087915409</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.04919831693722232</v>
+        <v>-0.05181555888397948</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.431372939399273</v>
+        <v>-1.437916044266162</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.292402736956368</v>
+        <v>2.288476874036235</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.809571308375364</v>
+        <v>-7.816114413242256</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02985661361967518</v>
+        <v>0.02723937167291801</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.24077326472612</v>
+        <v>-1.247316369593009</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.409577602447897</v>
+        <v>2.405651739527763</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960985</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.560571509691782</v>
+        <v>-7.567114614558675</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1423628743167664</v>
+        <v>0.1397456323700093</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.24077326472612</v>
+        <v>-1.247316369593009</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.422483943671556</v>
+        <v>2.418558080751422</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.666161499464887</v>
+        <v>-7.67270460433178</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.02784905119169423</v>
+        <v>-0.03046629313845095</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.346363254499224</v>
+        <v>-1.352906359366113</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.231154020208474</v>
+        <v>2.227228157288341</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.684896401583484</v>
+        <v>-7.691439506450377</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01320132983795341</v>
+        <v>0.01058408789119625</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.351959264159355</v>
+        <v>-1.358502369026245</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.276340756289482</v>
+        <v>2.272414893369348</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033368671081</v>
+        <v>3.760333686710808</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.536956360175885</v>
+        <v>-7.543499465042777</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04750157628717444</v>
+        <v>-0.05011881823393161</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.331638348250798</v>
+        <v>-1.338181453117687</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.168654383146449</v>
+        <v>2.164728520226316</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.483986837921896</v>
+        <v>-7.490529942788789</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.0350277536390573</v>
+        <v>-0.03764499558581402</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.278668825996809</v>
+        <v>-1.285211930863698</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.191722110245364</v>
+        <v>2.187796247325231</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098108</v>
+        <v>3.729969716098106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.440438431151206</v>
+        <v>-7.446981536018098</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.02456900302587428</v>
+        <v>-0.027186244972631</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.278668825996809</v>
+        <v>-1.285211930863698</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.184761498150271</v>
+        <v>2.180835635230137</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.782922533493417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.198290037697348</v>
+        <v>-7.20483314256424</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.08675270873681207</v>
+        <v>0.08413546679005535</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.278668825996809</v>
+        <v>-1.285211930863698</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.199223852531414</v>
+        <v>2.195297989611281</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722815</v>
+        <v>3.828551486722813</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.090030900574826</v>
+        <v>-7.096574005441719</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1245884840450158</v>
+        <v>0.121971242098259</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.278668825996809</v>
+        <v>-1.285211930863698</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.193755972990609</v>
+        <v>2.189830110070476</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792045</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.966739765757695</v>
+        <v>-6.973282870624588</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1714030319824453</v>
+        <v>0.1687857900356882</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.155377691179678</v>
+        <v>-1.161920796046568</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.265228747891464</v>
+        <v>2.261302884971331</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919906</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.945590566854252</v>
+        <v>-6.952133671721144</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1875636897811477</v>
+        <v>0.1849464478343905</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.134228492276235</v>
+        <v>-1.140771597143124</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.285619245470855</v>
+        <v>2.281693382550722</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.701825124870807</v>
+        <v>-6.7083682297377</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2808505749215762</v>
+        <v>0.278233332974819</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.134228492276235</v>
+        <v>-1.140771597143124</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.281399953817906</v>
+        <v>2.277474090897773</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057524</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.600062304593513</v>
+        <v>-6.606605409460405</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.32368001695251</v>
+        <v>0.3210627750057529</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.121009423883806</v>
+        <v>-1.127552528750696</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.291455708773379</v>
+        <v>2.287529845853246</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.350211910644438</v>
+        <v>-6.356755015511331</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4163622495158421</v>
+        <v>0.4137450075690849</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.121009423883806</v>
+        <v>-1.127552528750696</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.284197783757081</v>
+        <v>2.280271920836948</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.174319818177005</v>
+        <v>-6.180862923043898</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4903182100234638</v>
+        <v>0.487700968076707</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.121009423883806</v>
+        <v>-1.127552528750696</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.28779690727773</v>
+        <v>2.283871044357597</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.002873355154541</v>
+        <v>-6.009416460021434</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5722243012870032</v>
+        <v>0.569607059340246</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9495629608613433</v>
+        <v>-0.9561060657282324</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.403992291145761</v>
+        <v>2.400066428225628</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.77376522263278</v>
+        <v>3.773765222632778</v>
       </c>
       <c r="C1922" t="n">
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.928583789416202</v>
+        <v>-5.935126894283095</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6009606051986358</v>
+        <v>0.5983433632518786</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.8752733951230041</v>
+        <v>-0.8818164999898932</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.447586508205062</v>
+        <v>2.443660645284929</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.864948047182268</v>
+        <v>-5.871491152049161</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6311097031465267</v>
+        <v>0.6284924611997695</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8116376528890695</v>
+        <v>-0.8181807577559587</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.49046275459974</v>
+        <v>2.486536891679607</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.821185865876426</v>
+        <v>-5.827728970743319</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6298088344526591</v>
+        <v>0.627191592505902</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8116376528890695</v>
+        <v>-0.8181807577559587</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.471657013383536</v>
+        <v>2.467731150463402</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242293</v>
+        <v>3.797694884242291</v>
       </c>
       <c r="C1925" t="n">
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.580755369071566</v>
+        <v>-5.587298473938459</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7277241097994804</v>
+        <v>0.7251068678527233</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.5712071560842092</v>
+        <v>-0.5777502609510984</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.617658388091329</v>
+        <v>2.613732525171196</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367684</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.508512800900371</v>
+        <v>-5.515055905767264</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.7605504509027785</v>
+        <v>0.7579332089560213</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.5712071560842092</v>
+        <v>-0.5777502609510984</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.62158770192615</v>
+        <v>2.617661839006016</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.455514478618984</v>
+        <v>-5.462057583485876</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7824283637326737</v>
+        <v>0.7798111217859165</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5158708970822704</v>
+        <v>-0.5224140019491595</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.655468041244653</v>
+        <v>2.651542178324519</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.346709593139257</v>
+        <v>-5.353252698006149</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8229483891445581</v>
+        <v>0.820331147197801</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5158708970822704</v>
+        <v>-0.5224140019491595</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.652466112464646</v>
+        <v>2.648540249544513</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675938</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.126688795102246</v>
+        <v>-5.133231899969139</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9125357453699765</v>
+        <v>0.9099185034232193</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.3746510520142902</v>
+        <v>-0.3811941568811793</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.738777056516049</v>
+        <v>2.734851193595915</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539949</v>
+        <v>3.843274527539947</v>
       </c>
       <c r="C1930" t="n">
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.993821106038968</v>
+        <v>-5.000364210905861</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9815770037971108</v>
+        <v>0.9789597618503536</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.3746510520142902</v>
+        <v>-0.3811941568811793</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.754671239317872</v>
+        <v>2.750745376397739</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.87364802267447</v>
+        <v>-4.880191127541362</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.030792081583212</v>
+        <v>1.028174839636455</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2544779686497912</v>
+        <v>-0.2610210735166804</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.827920933776873</v>
+        <v>2.82399507085674</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576994</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.728975877574732</v>
+        <v>-4.735518982441625</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.098749042184547</v>
+        <v>1.09613180023779</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1098058235500538</v>
+        <v>-0.1163489284169429</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.924812323398156</v>
+        <v>2.920886460478022</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.788850704932424</v>
+        <v>-4.795393809799317</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.060836602642896</v>
+        <v>1.058219360696139</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1696806509077459</v>
+        <v>-0.1762237557746351</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.874924918384966</v>
+        <v>2.870999055464833</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.999133802252179</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.702051207153416</v>
+        <v>-4.708594312020309</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.117956895077065</v>
+        <v>1.115339653130308</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1696806509077459</v>
+        <v>-0.1762237557746351</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.897325411707532</v>
+        <v>2.893399548787399</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.999206203625592</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.704520913615222</v>
+        <v>-4.711064018482115</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.117041413865755</v>
+        <v>1.114424171918998</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1721503573695521</v>
+        <v>-0.1786934622364412</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.895915989203861</v>
+        <v>2.891990126283727</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>3.010213126100294</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.772891099939232</v>
+        <v>-4.779434204806125</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.100700261810853</v>
+        <v>1.098083019864096</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1628746583333371</v>
+        <v>-0.1694177632002263</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.912488331100291</v>
+        <v>2.908562468180158</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508366</v>
       </c>
       <c r="C1937" t="n">
         <v>3.000649834732185</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.881429280855366</v>
+        <v>-4.887972385722259</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.047721698076291</v>
+        <v>1.045104456129534</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1628746583333371</v>
+        <v>-0.1694177632002263</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.902925039732183</v>
+        <v>2.898999176812049</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417702</v>
+        <v>3.7109067314177</v>
       </c>
       <c r="C1938" t="n">
         <v>2.825359399772572</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.856798408577677</v>
+        <v>-4.83455323456023</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.8822836120277533</v>
+        <v>0.8911816816347322</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1628746583333371</v>
+        <v>-0.1694177632002263</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.727634604772569</v>
+        <v>2.723708741852436</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
         <v>2.829926631764359</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.681324148785207</v>
+        <v>-4.65907897476776</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.9570405479365289</v>
+        <v>0.9659386175435078</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1628746583333371</v>
+        <v>-0.1694177632002263</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.732201836764357</v>
+        <v>2.728275973844224</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.805668660525567</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.792260401426456</v>
+        <v>-4.770015227409009</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.8884080756412365</v>
+        <v>0.8973061452482154</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1628746583333371</v>
+        <v>-0.1694177632002263</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.707943865525564</v>
+        <v>2.704018002605431</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111292</v>
+        <v>3.77321029711129</v>
       </c>
       <c r="C1941" t="n">
         <v>2.808800045745472</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.800542475571515</v>
+        <v>-4.778297301554067</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8882266312031186</v>
+        <v>0.8971247008100975</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1711567324783955</v>
+        <v>-0.1776998373452847</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.706106006258435</v>
+        <v>2.702180143338301</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264159</v>
       </c>
       <c r="C1942" t="n">
         <v>2.818972432177604</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.740689856367791</v>
+        <v>-4.718444682350344</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9223400653167402</v>
+        <v>0.9312381349237191</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1711567324783955</v>
+        <v>-0.1776998373452847</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.716278392690567</v>
+        <v>2.712352529770434</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742295</v>
       </c>
       <c r="C1943" t="n">
         <v>2.813918702751465</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.654446393341414</v>
+        <v>-4.632201219323966</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9517837211011515</v>
+        <v>0.9606817907081306</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1711567324783955</v>
+        <v>-0.1776998373452847</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.711224663264427</v>
+        <v>2.707298800344294</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.80569447819599</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.699753212740394</v>
+        <v>-4.677508038722946</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9254367687860852</v>
+        <v>0.9343348383930641</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2119668954876263</v>
+        <v>-0.2185100003545155</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.678514340903415</v>
+        <v>2.674588477983281</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.806246351229092</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.728786317442695</v>
+        <v>-4.706541143425247</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9143753999382662</v>
+        <v>0.9232734695452454</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2119668954876263</v>
+        <v>-0.2185100003545155</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.679066213936516</v>
+        <v>2.675140351016383</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.735519043120457</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.635975835991835</v>
+        <v>-4.613730661974388</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8807722844099759</v>
+        <v>0.8896703540169548</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.119156414036767</v>
+        <v>-0.1256995189036561</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.664025194698397</v>
+        <v>2.660099331778264</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.737392519045058</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.680365305321263</v>
+        <v>-4.658120131303815</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8648899726028056</v>
+        <v>0.8737880422097846</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.1635458833661946</v>
+        <v>-0.1700889882330838</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.639264989025342</v>
+        <v>2.635339126105208</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.732468227556781</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.567694087085012</v>
+        <v>-4.545448913067565</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9050341684090286</v>
+        <v>0.9139322380160078</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.05087466512994443</v>
+        <v>-0.05741776999683357</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.701943428478815</v>
+        <v>2.698017565558681</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.737959523387449</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.455317085902339</v>
+        <v>-4.433071911884892</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.955476264712765</v>
+        <v>0.9643743343197442</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.05087466512994443</v>
+        <v>-0.05741776999683357</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.707434724309482</v>
+        <v>2.703508861389349</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.749456725155988</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.483097483803692</v>
+        <v>-4.460852309786245</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9558613073207631</v>
+        <v>0.9647593769277421</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.07865506303129749</v>
+        <v>-0.08519816789818663</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.702263687337209</v>
+        <v>2.698337824417076</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705323</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.587812445156641</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.566098764828971</v>
+        <v>-4.543853590811524</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7610165149113048</v>
+        <v>0.7699145845182838</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.09722594755847125</v>
+        <v>-0.1037690524253604</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.529476876621558</v>
+        <v>2.525551013701425</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729268</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.707962105875847</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.674712843272302</v>
+        <v>-4.652467669254855</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8377205442531781</v>
+        <v>0.846618613860157</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.09722594755847125</v>
+        <v>-0.1037690524253604</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.649626537340764</v>
+        <v>2.645700674420631</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190767</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
         <v>2.722475131978169</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.761311426253405</v>
+        <v>-4.739066252235958</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8175941371630597</v>
+        <v>0.8264922067700389</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.09722594755847125</v>
+        <v>-0.1037690524253604</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.664139563443087</v>
+        <v>2.660213700522954</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.719894573320538</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.722927763695254</v>
+        <v>-4.700682589677807</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.830367043528689</v>
+        <v>0.8392651131356679</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.05884228500032007</v>
+        <v>-0.06538538986720921</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.684589202320347</v>
+        <v>2.680663339400213</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532484</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
         <v>2.71662360216584</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.545811433660088</v>
+        <v>-4.52356625964264</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.8979426043880574</v>
+        <v>0.9068406739950363</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.05884228500032007</v>
+        <v>-0.06538538986720921</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.681318231165648</v>
+        <v>2.677392368245515</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.7413284487939</v>
       </c>
       <c r="C1956" t="n">
         <v>2.717306993927753</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.590903678493634</v>
+        <v>-4.568658504476186</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.8805890982165521</v>
+        <v>0.889487167823531</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1207383281697099</v>
+        <v>-0.127281433036599</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.644863997025928</v>
+        <v>2.640938134105794</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.711093969234168</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.411528257254866</v>
+        <v>-4.389283083237419</v>
       </c>
       <c r="E1957" t="n">
-        <v>0.9461262420184735</v>
+        <v>0.9550243116254524</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.03603843000100881</v>
+        <v>0.02949532513411968</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.732717027234773</v>
+        <v>2.728791164314639</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.691901424565757</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.456542470775472</v>
+        <v>-4.434297296758024</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.908928011941821</v>
+        <v>0.9178260815488</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.005689534686404207</v>
+        <v>-0.0008535701804849305</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.6953151453776</v>
+        <v>2.691389282457467</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509534</v>
       </c>
       <c r="C1959" t="n">
         <v>2.697592986904703</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.723546981047907</v>
+        <v>-4.701301807030459</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8078177701717928</v>
+        <v>0.8167158397787717</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1886735033565444</v>
+        <v>-0.1952166082234335</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.584388884890777</v>
+        <v>2.580463021970643</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760806</v>
       </c>
       <c r="C1960" t="n">
         <v>2.696796908801204</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.824744762485079</v>
+        <v>-4.802499588467632</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7665425794934251</v>
+        <v>0.775440649100404</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2570823169018636</v>
+        <v>-0.2636254217687527</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.542547518660087</v>
+        <v>2.538621655739953</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.694396870355521</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.792269176314307</v>
+        <v>-4.77002400229686</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.7771327755160506</v>
+        <v>0.7860308451230296</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2570823169018636</v>
+        <v>-0.2636254217687527</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.540147480214404</v>
+        <v>2.53622161729427</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.690921589563766</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.77323104860701</v>
+        <v>-4.750985874589563</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.7812727458072146</v>
+        <v>0.7901708154141935</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3152659282330581</v>
+        <v>-0.3218090330999472</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.501762032623931</v>
+        <v>2.497836169703798</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131249</v>
+        <v>3.731064473131247</v>
       </c>
       <c r="C1963" t="n">
         <v>2.868503458502447</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.804357679757628</v>
+        <v>-4.782112505740181</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9464039622856477</v>
+        <v>0.9553020318926266</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3152659282330581</v>
+        <v>-0.3218090330999472</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.679343901562612</v>
+        <v>2.675418038642479</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.86933678748858</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.818224441091546</v>
+        <v>-4.795979267074099</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9416905867382142</v>
+        <v>0.9505886563451931</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.353123844966881</v>
+        <v>-0.3596669498337702</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.657462480508452</v>
+        <v>2.653536617588319</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.875345317885506</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.838481739620504</v>
+        <v>-4.816236565603057</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.939596197723557</v>
+        <v>0.9484942673305359</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.353123844966881</v>
+        <v>-0.3596669498337702</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.663471010905378</v>
+        <v>2.659545147985245</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519905</v>
       </c>
       <c r="C1966" t="n">
         <v>2.954497965677528</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.690738769385502</v>
+        <v>-4.668493595368054</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.07784603360958</v>
+        <v>1.086744103216559</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1853164877319979</v>
+        <v>-0.191859592598887</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.84330807303833</v>
+        <v>2.839382210118196</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.957291587209009</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.792753451916723</v>
+        <v>-4.770508277899276</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.039833782128572</v>
+        <v>1.048731851735551</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1853164877319979</v>
+        <v>-0.191859592598887</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.846101694569811</v>
+        <v>2.842175831649677</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394728</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
         <v>2.957953935600667</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.786600745863939</v>
+        <v>-4.764355571846491</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.042957212941344</v>
+        <v>1.051855282548323</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1791637816792136</v>
+        <v>-0.1857068865461027</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.85045566659314</v>
+        <v>2.846529803673006</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.957034412340778</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.80341004401444</v>
+        <v>-4.781164869996993</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.035313970421254</v>
+        <v>1.044212040028233</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1959730798297152</v>
+        <v>-0.2025161846966044</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.839450564442949</v>
+        <v>2.835524701522815</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>3.023369966137599</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.741112045238318</v>
+        <v>-4.718866871220871</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.126568723728524</v>
+        <v>1.135466793335503</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1959730798297152</v>
+        <v>-0.2025161846966044</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.90578611823977</v>
+        <v>2.901860255319636</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
         <v>2.731950838526997</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.53932184757316</v>
+        <v>-4.517076673555713</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9158656751839849</v>
+        <v>0.9247637447909638</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.002045112339439159</v>
+        <v>-0.004497992527449979</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.73317790593066</v>
+        <v>2.729252043010527</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852418</v>
       </c>
       <c r="C1972" t="n">
         <v>2.802241070849172</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.479431165930567</v>
+        <v>-4.45718599191312</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.010112180163197</v>
+        <v>1.019010249770176</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.06193579398203264</v>
+        <v>0.0553926891151435</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.839402547238392</v>
+        <v>2.835476684318258</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.816868806965215</v>
       </c>
       <c r="D1973" t="n">
-        <v>-4.577171710555541</v>
+        <v>-4.554926536538094</v>
       </c>
       <c r="E1973" t="n">
-        <v>0.9856436984292514</v>
+        <v>0.9945417680362303</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.04604651584905245</v>
+        <v>0.03950341098216331</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.844496716474647</v>
+        <v>2.840570853554514</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.815404787789887</v>
       </c>
       <c r="D1974" t="n">
-        <v>-4.753509470678471</v>
+        <v>-4.731264296661023</v>
       </c>
       <c r="E1974" t="n">
-        <v>0.9136445752047513</v>
+        <v>0.9225426448117302</v>
       </c>
       <c r="F1974" t="n">
-        <v>-0.1302912442738769</v>
+        <v>-0.1368343491407661</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.737230041225561</v>
+        <v>2.733304178305428</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.813896405829816</v>
       </c>
       <c r="D1975" t="n">
-        <v>-4.681963147901594</v>
+        <v>-4.659717973884146</v>
       </c>
       <c r="E1975" t="n">
-        <v>0.9407547223554307</v>
+        <v>0.9496527919624096</v>
       </c>
       <c r="F1975" t="n">
-        <v>-0.1302912442738769</v>
+        <v>-0.1368343491407661</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.73572165926549</v>
+        <v>2.731795796345356</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.836023391024959</v>
+        <v>3.836023391024957</v>
       </c>
       <c r="C1976" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1976" t="n">
-        <v>-4.637590016263025</v>
+        <v>-4.615344842245578</v>
       </c>
       <c r="E1976" t="n">
-        <v>0.9583668424462943</v>
+        <v>0.9672649120532733</v>
       </c>
       <c r="F1976" t="n">
-        <v>-0.08591811263530835</v>
+        <v>-0.09246121750219749</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.762208405684067</v>
+        <v>2.758282542763934</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821591150863221</v>
+        <v>3.821591150863219</v>
       </c>
       <c r="C1977" t="n">
         <v>2.813759273265252</v>
       </c>
       <c r="D1977" t="n">
-        <v>-4.629636045968253</v>
+        <v>-4.607390871950805</v>
       </c>
       <c r="E1977" t="n">
-        <v>0.961548430564203</v>
+        <v>0.9704465001711822</v>
       </c>
       <c r="F1977" t="n">
-        <v>-0.08591811263530835</v>
+        <v>-0.09246121750219749</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.762208405684067</v>
+        <v>2.758282542763934</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.83304018194758</v>
+        <v>3.833040181947578</v>
       </c>
       <c r="C1978" t="n">
         <v>2.820141030293057</v>
       </c>
       <c r="D1978" t="n">
-        <v>-4.581980315407197</v>
+        <v>-4.55973514138975</v>
       </c>
       <c r="E1978" t="n">
-        <v>0.98699247981643</v>
+        <v>0.9958905494234092</v>
       </c>
       <c r="F1978" t="n">
-        <v>-0.0382623820742527</v>
+        <v>-0.04480548694114184</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.797183601048505</v>
+        <v>2.793257738128372</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822707244326873</v>
+        <v>3.822707244326871</v>
       </c>
       <c r="C1979" t="n">
         <v>2.825033403667781</v>
       </c>
       <c r="D1979" t="n">
-        <v>-4.454296005612901</v>
+        <v>-4.432050831595453</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.042958577108873</v>
+        <v>1.051856646715852</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.08942192772004376</v>
+        <v>0.08287882285315462</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.878686560299808</v>
+        <v>2.874760697379674</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828837911314548</v>
+        <v>3.828837911314547</v>
       </c>
       <c r="C1980" t="n">
         <v>2.811788076143654</v>
       </c>
       <c r="D1980" t="n">
-        <v>-4.51496259601529</v>
+        <v>-4.492717421997843</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.00544661342379</v>
+        <v>1.014344683030769</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.007723611001510089</v>
+        <v>0.001180506134620951</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.81642224274456</v>
+        <v>2.812496379824426</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816866067690024</v>
+        <v>3.816866067690023</v>
       </c>
       <c r="C1981" t="n">
         <v>2.815885778754282</v>
       </c>
       <c r="D1981" t="n">
-        <v>-4.470124194406892</v>
+        <v>-4.447879020389444</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.027479676677778</v>
+        <v>1.036377746284757</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.01226704394637956</v>
+        <v>0.005723939079490425</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.82324600512211</v>
+        <v>2.819320142201977</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817961388674307</v>
+        <v>3.817961388674306</v>
       </c>
       <c r="C1982" t="n">
         <v>2.82004671838536</v>
       </c>
       <c r="D1982" t="n">
-        <v>-4.57088283016389</v>
+        <v>-4.548637656146442</v>
       </c>
       <c r="E1982" t="n">
-        <v>0.9913371620060567</v>
+        <v>1.000235231613036</v>
       </c>
       <c r="F1982" t="n">
-        <v>-0.07655852478062586</v>
+        <v>-0.083101629647515</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.774111603516985</v>
+        <v>2.770185740596852</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826713779163216</v>
+        <v>3.826713779163215</v>
       </c>
       <c r="C1983" t="n">
         <v>2.825926320913197</v>
       </c>
       <c r="D1983" t="n">
-        <v>-4.526679993077989</v>
+        <v>-4.504434819060542</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.014897899368254</v>
+        <v>1.023795968975233</v>
       </c>
       <c r="F1983" t="n">
-        <v>-0.03235568769472541</v>
+        <v>-0.03889879256161455</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.806512908296362</v>
+        <v>2.802587045376229</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838228663022901</v>
+        <v>3.8382286630229</v>
       </c>
       <c r="C1984" t="n">
         <v>2.824336321382445</v>
       </c>
       <c r="D1984" t="n">
-        <v>-4.563659020741432</v>
+        <v>-4.541413846723985</v>
       </c>
       <c r="E1984" t="n">
-        <v>0.9985162887721244</v>
+        <v>1.007414358379103</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.004618214096605122</v>
+        <v>-0.001924890770284016</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.827107249840408</v>
+        <v>2.823181386920275</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863924114042136</v>
+        <v>3.863924114042134</v>
       </c>
       <c r="C1985" t="n">
         <v>2.875584086565484</v>
       </c>
       <c r="D1985" t="n">
-        <v>-4.583717099606273</v>
+        <v>-4.561471925588825</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.041740822409228</v>
+        <v>1.050638892016207</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.004618214096605122</v>
+        <v>-0.001924890770284016</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.878355015023448</v>
+        <v>2.874429152103315</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865367715078278</v>
+        <v>3.865367715078277</v>
       </c>
       <c r="C1986" t="n">
         <v>2.874024791159738</v>
       </c>
       <c r="D1986" t="n">
-        <v>-4.543786426428382</v>
+        <v>-4.521541252410935</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.056153796274637</v>
+        <v>1.065051865881616</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.04454888727449546</v>
+        <v>0.03800578240760633</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.900754123524435</v>
+        <v>2.896828260604302</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864518876232395</v>
+        <v>3.864518876232394</v>
       </c>
       <c r="C1987" t="n">
         <v>2.868973019398008</v>
       </c>
       <c r="D1987" t="n">
-        <v>-4.503316078865677</v>
+        <v>-4.48107090484823</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.067290163537989</v>
+        <v>1.076188233144968</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.08501923483720042</v>
+        <v>0.07847612997031128</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.919984560300328</v>
+        <v>2.916058697380195</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842576394162111</v>
+        <v>3.842576394162109</v>
       </c>
       <c r="C1988" t="n">
         <v>2.886160423490713</v>
       </c>
       <c r="D1988" t="n">
-        <v>-4.438091897738472</v>
+        <v>-4.415846723721025</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.110567240081576</v>
+        <v>1.119465309688555</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.150243415964406</v>
+        <v>0.1437003110975169</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.976306473069356</v>
+        <v>2.972380610149223</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840090220639816</v>
+        <v>3.840090220639814</v>
       </c>
       <c r="C1989" t="n">
         <v>2.882121395789993</v>
       </c>
       <c r="D1989" t="n">
-        <v>-4.488586188095528</v>
+        <v>-4.466341014078081</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.086330496238034</v>
+        <v>1.095228565845013</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.1052226788383318</v>
+        <v>0.09867957397144267</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.945255003092992</v>
+        <v>2.941329140172859</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845198842749919</v>
+        <v>3.845198842749917</v>
       </c>
       <c r="C1990" t="n">
         <v>2.883378188121233</v>
       </c>
       <c r="D1990" t="n">
-        <v>-4.508697844130237</v>
+        <v>-4.486452670112789</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.079542626155391</v>
+        <v>1.08844069576237</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.116250023835751</v>
+        <v>0.1097069189688619</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.953128202422684</v>
+        <v>2.949202339502551</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828690479393544</v>
+        <v>3.828690479393543</v>
       </c>
       <c r="C1991" t="n">
         <v>3.043935959142444</v>
       </c>
       <c r="D1991" t="n">
-        <v>-4.606378423402883</v>
+        <v>-4.584133249385435</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.201028165467543</v>
+        <v>1.209926235074522</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.005546828495562206</v>
+        <v>-0.0009962763713269318</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.047264056239781</v>
+        <v>3.043338193319648</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813251854714882</v>
+        <v>3.81325185471488</v>
       </c>
       <c r="C1992" t="n">
         <v>3.164048868360261</v>
       </c>
       <c r="D1992" t="n">
-        <v>-4.58258685479674</v>
+        <v>-4.560341680779293</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.330657702127818</v>
+        <v>1.339555771734797</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.02933839710170449</v>
+        <v>0.02279529223481536</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.181651906621284</v>
+        <v>3.177726043701151</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81425976175601</v>
+        <v>3.814259761756008</v>
       </c>
       <c r="C1993" t="n">
         <v>3.15575684437412</v>
       </c>
       <c r="D1993" t="n">
-        <v>-4.619341273358462</v>
+        <v>-4.597096099341015</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.307663910716988</v>
+        <v>1.316561980323967</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.02933839710170449</v>
+        <v>0.02279529223481536</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.173359882635143</v>
+        <v>3.169434019715009</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803426852654185</v>
+        <v>3.803426852654183</v>
       </c>
       <c r="C1994" t="n">
         <v>3.1539500399579</v>
       </c>
       <c r="D1994" t="n">
-        <v>-4.615006970301414</v>
+        <v>-4.592761796283967</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.307590827523586</v>
+        <v>1.316488897130565</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.1809885004209084</v>
+        <v>0.1744453955540193</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.262543140210445</v>
+        <v>3.258617277290312</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796293177717115</v>
+        <v>3.796293177717113</v>
       </c>
       <c r="C1995" t="n">
         <v>3.171504445684691</v>
       </c>
       <c r="D1995" t="n">
-        <v>-4.606114508908131</v>
+        <v>-4.583869334890684</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.328702217807691</v>
+        <v>1.33760028741467</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.1809885004209084</v>
+        <v>0.1744453955540193</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.280097545937236</v>
+        <v>3.276171683017103</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794453975702623</v>
+        <v>3.794453975702622</v>
       </c>
       <c r="C1996" t="n">
         <v>3.163359493089275</v>
       </c>
       <c r="D1996" t="n">
-        <v>-4.774590625878009</v>
+        <v>-4.752345451860561</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.253166818424324</v>
+        <v>1.262064888031303</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.1530406647043276</v>
+        <v>0.1464975598374385</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.255183891911872</v>
+        <v>3.251258028991738</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795603100539968</v>
+        <v>3.795603100539966</v>
       </c>
       <c r="C1997" t="n">
         <v>3.233772154546119</v>
       </c>
       <c r="D1997" t="n">
-        <v>-4.624103944281958</v>
+        <v>-4.601858770264511</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.383774152519588</v>
+        <v>1.392672222126567</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.1143922945468981</v>
+        <v>0.107849189680009</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.302407531274258</v>
+        <v>3.298481668354124</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.757881648454559</v>
+        <v>3.757881648454556</v>
       </c>
       <c r="C1998" t="n">
-        <v>3.17564340766071</v>
+        <v>3.224436177043023</v>
       </c>
       <c r="D1998" t="n">
-        <v>-4.685047028046715</v>
+        <v>-4.663889067788984</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.301268172128276</v>
+        <v>1.358524125613682</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.1143922945468981</v>
+        <v>0.107849189680009</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.244278784388849</v>
+        <v>3.289145690851029</v>
       </c>
     </row>
   </sheetData>
